--- a/uid/103A机房建模信息整理xlsx.xlsx
+++ b/uid/103A机房建模信息整理xlsx.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="414" uniqueCount="195">
   <si>
     <t>设备名称</t>
   </si>
@@ -35,469 +35,583 @@
     <t>uid</t>
   </si>
   <si>
+    <t>103A机房J列头柜B路</t>
+  </si>
+  <si>
+    <t>N2_S0_E190</t>
+  </si>
+  <si>
+    <t>103A机房J列头柜A路</t>
+  </si>
+  <si>
+    <t>N2_S0_E189</t>
+  </si>
+  <si>
+    <t>103A机房I列头柜B路</t>
+  </si>
+  <si>
+    <t>N2_S0_E188</t>
+  </si>
+  <si>
+    <t>103A机房I列头柜A路</t>
+  </si>
+  <si>
+    <t>N2_S0_E187</t>
+  </si>
+  <si>
+    <t>103A机房H列头柜B路</t>
+  </si>
+  <si>
+    <t>N2_S0_E186</t>
+  </si>
+  <si>
+    <t>103A机房H列头柜A路</t>
+  </si>
+  <si>
+    <t>N2_S0_E185</t>
+  </si>
+  <si>
+    <t>103A机房G列头柜B路</t>
+  </si>
+  <si>
+    <t>N2_S0_E184</t>
+  </si>
+  <si>
+    <t>103A机房G列头柜A路</t>
+  </si>
+  <si>
+    <t>N2_S0_E183</t>
+  </si>
+  <si>
+    <t>103A机房F列头柜B路</t>
+  </si>
+  <si>
+    <t>N2_S0_E182</t>
+  </si>
+  <si>
+    <t>103A机房E列头柜A路</t>
+  </si>
+  <si>
+    <t>N2_S0_E181</t>
+  </si>
+  <si>
+    <t>103A机房E列头柜B路</t>
+  </si>
+  <si>
+    <t>N2_S0_E40</t>
+  </si>
+  <si>
+    <t>103A机房F列头柜A路</t>
+  </si>
+  <si>
+    <t>N2_S0_E39</t>
+  </si>
+  <si>
+    <t>103A机房D列头柜B路</t>
+  </si>
+  <si>
+    <t>N2_S0_E38</t>
+  </si>
+  <si>
+    <t>103A机房D列头柜A路</t>
+  </si>
+  <si>
+    <t>N2_S0_E37</t>
+  </si>
+  <si>
+    <t>103A机房C列头柜B路</t>
+  </si>
+  <si>
+    <t>N2_S0_E36</t>
+  </si>
+  <si>
+    <t>103A机房C列头柜A路</t>
+  </si>
+  <si>
+    <t>N2_S0_E35</t>
+  </si>
+  <si>
+    <t>103A机房B列头柜B路</t>
+  </si>
+  <si>
+    <t>N2_S0_E34</t>
+  </si>
+  <si>
+    <t>103A机房B列头柜A路</t>
+  </si>
+  <si>
+    <t>N2_S0_E33</t>
+  </si>
+  <si>
+    <t>103A机房A列头柜B路</t>
+  </si>
+  <si>
+    <t>N2_S0_E32</t>
+  </si>
+  <si>
+    <t>103A机房A列头柜A路</t>
+  </si>
+  <si>
+    <t>N2_S0_E31</t>
+  </si>
+  <si>
+    <t>1F IDC机房1#空调</t>
+  </si>
+  <si>
+    <t>回风湿度设定点（%）</t>
+  </si>
+  <si>
+    <t>N2_S0_E1_A27</t>
+  </si>
+  <si>
+    <t>回风温度设定点（℃）</t>
+  </si>
+  <si>
+    <t>N2_S0_E1_A28</t>
+  </si>
+  <si>
+    <t>远程平均温度设定点（℃）</t>
+  </si>
+  <si>
+    <t>N2_S0_E1_A30</t>
+  </si>
+  <si>
+    <t>远程最高温度设定点（℃）</t>
+  </si>
+  <si>
+    <t>N2_S0_E1_A31</t>
+  </si>
+  <si>
+    <t>1F IDC机房2#空调</t>
+  </si>
+  <si>
+    <t>N2_S0_E2_A27</t>
+  </si>
+  <si>
+    <t>N2_S0_E2_A28</t>
+  </si>
+  <si>
+    <t>N2_S0_E2_A30</t>
+  </si>
+  <si>
+    <t>N2_S0_E2_A31</t>
+  </si>
+  <si>
+    <t>1F IDC机房3#空调</t>
+  </si>
+  <si>
+    <t>N2_S0_E3_A27</t>
+  </si>
+  <si>
+    <t>N2_S0_E3_A28</t>
+  </si>
+  <si>
+    <t>N2_S0_E3_A30</t>
+  </si>
+  <si>
+    <t>N2_S0_E3_A31</t>
+  </si>
+  <si>
+    <t>1F IDC机房4#空调</t>
+  </si>
+  <si>
+    <t>N2_S0_E4_A27</t>
+  </si>
+  <si>
+    <t>N2_S0_E4_A28</t>
+  </si>
+  <si>
+    <t>N2_S0_E4_A30</t>
+  </si>
+  <si>
+    <t>N2_S0_E4_A31</t>
+  </si>
+  <si>
+    <t>1F IDC机房5#空调</t>
+  </si>
+  <si>
+    <t>N2_S0_E5_A27</t>
+  </si>
+  <si>
+    <t>N2_S0_E5_A28</t>
+  </si>
+  <si>
+    <t>N2_S0_E5_A30</t>
+  </si>
+  <si>
+    <t>N2_S0_E5_A31</t>
+  </si>
+  <si>
+    <t>1F IDC机房6#空调</t>
+  </si>
+  <si>
+    <t>N2_S0_E6_A27</t>
+  </si>
+  <si>
+    <t>N2_S0_E6_A28</t>
+  </si>
+  <si>
+    <t>N2_S0_E6_A30</t>
+  </si>
+  <si>
+    <t>N2_S0_E6_A31</t>
+  </si>
+  <si>
+    <t>1F IDC机房7#空调</t>
+  </si>
+  <si>
+    <t>N2_S0_E7_A27</t>
+  </si>
+  <si>
+    <t>N2_S0_E7_A28</t>
+  </si>
+  <si>
+    <t>N2_S0_E7_A30</t>
+  </si>
+  <si>
+    <t>N2_S0_E7_A31</t>
+  </si>
+  <si>
+    <t>1F IDC机房8#空调</t>
+  </si>
+  <si>
+    <t>N2_S0_E8_A27</t>
+  </si>
+  <si>
+    <t>N2_S0_E8_A28</t>
+  </si>
+  <si>
+    <t>N2_S0_E8_A30</t>
+  </si>
+  <si>
+    <t>N2_S0_E8_A31</t>
+  </si>
+  <si>
+    <t>1F IDC机房9#空调</t>
+  </si>
+  <si>
+    <t>N2_S0_E9_A27</t>
+  </si>
+  <si>
+    <t>N2_S0_E9_A28</t>
+  </si>
+  <si>
+    <t>N2_S0_E9_A30</t>
+  </si>
+  <si>
+    <t>N2_S0_E9_A31</t>
+  </si>
+  <si>
     <t>1F IDC机房热通道33#温湿度</t>
   </si>
   <si>
-    <t>4f133ebb-4d48-4509-9115-fd007f6bf901</t>
+    <t>1#温度</t>
+  </si>
+  <si>
+    <t>a7217828_ed16_4ffa_b789_04ada92a2e75</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>1#湿度</t>
+  </si>
+  <si>
+    <t>52664cb3_a254_46c0_9674_777ef3b68793</t>
   </si>
   <si>
     <t>1F IDC机房冷通道32#温湿度</t>
   </si>
   <si>
-    <t>05a5e35e-a1ad-4736-b733-403f64c11099</t>
+    <t>a38944a0_b951_45b2_a13c_13a6fa9223e4</t>
+  </si>
+  <si>
+    <t>600edf85_f3ec_46e5_a811_855f82ae07f4</t>
   </si>
   <si>
     <t>1F IDC机房热通道31#温湿度</t>
   </si>
   <si>
-    <t>674fffca-7b8e-4342-a4d4-5159ab87519b</t>
+    <t>4fe07996_cd59_4771_ab80_bab15210849b</t>
+  </si>
+  <si>
+    <t>b111676c_bfed_4fca_a23e_91774e9736fa</t>
   </si>
   <si>
     <t>1F IDC机房冷通道30#温湿度</t>
   </si>
   <si>
-    <t>f4a698e8-1222-4f5c-b4af-bf7d750e2040</t>
+    <t>44686a4e_336a_471f_9f04_abfe29f12c8a</t>
+  </si>
+  <si>
+    <t>24e69074_556e_421e_88bc_d983f21e2a46</t>
   </si>
   <si>
     <t>1F IDC机房热通道29#温湿度</t>
   </si>
   <si>
-    <t>d57c1e45-e292-4fd7-b01d-670088cd3e17</t>
+    <t>0ab54859_d564_4e3d_9810_2d74a26d007d</t>
+  </si>
+  <si>
+    <t>25c42ff2_2278_42ca_b97c_43f82cf29737</t>
   </si>
   <si>
     <t>1F IDC机房冷通道28#温湿度</t>
   </si>
   <si>
-    <t>a51b87eb-529b-42f1-b988-2869353c2cef</t>
+    <t>f50dd4c9_c782_4c40_81e6_14dcfd755436</t>
+  </si>
+  <si>
+    <t>dd6f7451_7a3d_4656_97ef_b350af38491a</t>
   </si>
   <si>
     <t>1F IDC机房热通道27#温湿度</t>
   </si>
   <si>
-    <t>45b591fe-d54c-4fec-b608-ce5b9932dcc6</t>
+    <t>bdb38c2a_f0c6_49c0_b62a_d4e0fc5fd0ea</t>
+  </si>
+  <si>
+    <t>b3582d8f_390a_4db6_8f42_68be2cad1339</t>
   </si>
   <si>
     <t>1F IDC机房冷通道26#温湿度</t>
   </si>
   <si>
-    <t>34dc121a-aa9a-4c7b-a59a-57915ddf8c3c</t>
+    <t>a10310ed_ff3a_4bdf_b02e_0362f5808958</t>
+  </si>
+  <si>
+    <t>0dc718ed_ea4c_4d82_be43_6d94b9943fa7</t>
   </si>
   <si>
     <t>1F IDC机房热通道25#温湿度</t>
   </si>
   <si>
-    <t>1dcae536-3d1b-4f49-a81a-cb39cbc44bfb</t>
+    <t>07bb7d1d_b635_4ca9_909c_7bdaf3ceab10</t>
+  </si>
+  <si>
+    <t>e8700958_d7b7_4050_874d_294fbe149531</t>
   </si>
   <si>
     <t>1F IDC机房冷通道24#温湿度</t>
   </si>
   <si>
-    <t>62875abb-b261-4fa2-af42-49413b25f637</t>
+    <t>be578260_b5e1_4e29_888f_4ba9d2c1b138</t>
+  </si>
+  <si>
+    <t>8e318fc0_0003_43c3_8817_0920307d4e1a</t>
   </si>
   <si>
     <t>1F IDC机房热通道23#温湿度</t>
   </si>
   <si>
-    <t>d95f6576-ad3e-4eca-bab8-10fb28738764</t>
-  </si>
-  <si>
-    <t>103A机房J列头柜B路</t>
-  </si>
-  <si>
-    <t>N2_S0_E190</t>
-  </si>
-  <si>
-    <t>103A机房J列头柜A路</t>
-  </si>
-  <si>
-    <t>N2_S0_E189</t>
-  </si>
-  <si>
-    <t>103A机房I列头柜B路</t>
-  </si>
-  <si>
-    <t>N2_S0_E188</t>
-  </si>
-  <si>
-    <t>103A机房I列头柜A路</t>
-  </si>
-  <si>
-    <t>N2_S0_E187</t>
-  </si>
-  <si>
-    <t>103A机房H列头柜B路</t>
-  </si>
-  <si>
-    <t>N2_S0_E186</t>
-  </si>
-  <si>
-    <t>103A机房H列头柜A路</t>
-  </si>
-  <si>
-    <t>N2_S0_E185</t>
-  </si>
-  <si>
-    <t>103A机房G列头柜B路</t>
-  </si>
-  <si>
-    <t>N2_S0_E184</t>
-  </si>
-  <si>
-    <t>103A机房G列头柜A路</t>
-  </si>
-  <si>
-    <t>N2_S0_E183</t>
-  </si>
-  <si>
-    <t>103A机房F列头柜B路</t>
-  </si>
-  <si>
-    <t>N2_S0_E182</t>
-  </si>
-  <si>
-    <t>103A机房E列头柜A路</t>
-  </si>
-  <si>
-    <t>N2_S0_E181</t>
+    <t>ad0a96f7_8d56_4120_b0fd_666f6419da54</t>
+  </si>
+  <si>
+    <t>50811f02_536c_4bdb_88f7_1769d6110ea1</t>
   </si>
   <si>
     <t>1F IDC机房热通道22#温湿度</t>
   </si>
   <si>
-    <t>N2_S0_E102</t>
+    <t>温度</t>
+  </si>
+  <si>
+    <t>N2_S0_E102_A1</t>
+  </si>
+  <si>
+    <t>湿度</t>
+  </si>
+  <si>
+    <t>N2_S0_E102_A2</t>
   </si>
   <si>
     <t>1F IDC机房热通道21#温湿度</t>
   </si>
   <si>
-    <t>N2_S0_E101</t>
+    <t>N2_S0_E101_A1</t>
+  </si>
+  <si>
+    <t>N2_S0_E101_A2</t>
   </si>
   <si>
     <t>1F IDC机房冷通道20#温湿度</t>
   </si>
   <si>
-    <t>N2_S0_E100</t>
+    <t>N2_S0_E100_A1</t>
+  </si>
+  <si>
+    <t>N2_S0_E100_A2</t>
   </si>
   <si>
     <t>1F IDC机房冷通道19#温湿度</t>
   </si>
   <si>
-    <t>N2_S0_E99</t>
+    <t>N2_S0_E99_A1</t>
+  </si>
+  <si>
+    <t>N2_S0_E99_A2</t>
   </si>
   <si>
     <t>1F IDC机房热通道18#温湿度</t>
   </si>
   <si>
-    <t>N2_S0_E98</t>
+    <t>N2_S0_E98_A1</t>
+  </si>
+  <si>
+    <t>N2_S0_E98_A2</t>
   </si>
   <si>
     <t>1F IDC机房热通道17#温湿度</t>
   </si>
   <si>
-    <t>N2_S0_E97</t>
+    <t>N2_S0_E97_A1</t>
+  </si>
+  <si>
+    <t>N2_S0_E97_A2</t>
   </si>
   <si>
     <t>1F IDC机房冷通道16#温湿度</t>
   </si>
   <si>
-    <t>N2_S0_E96</t>
+    <t>N2_S0_E96_A1</t>
+  </si>
+  <si>
+    <t>N2_S0_E96_A2</t>
   </si>
   <si>
     <t>1F IDC机房冷通道15#温湿度</t>
   </si>
   <si>
-    <t>N2_S0_E95</t>
+    <t>N2_S0_E95_A1</t>
+  </si>
+  <si>
+    <t>N2_S0_E95_A2</t>
   </si>
   <si>
     <t>1F IDC机房热通道14#温湿度</t>
   </si>
   <si>
-    <t>N2_S0_E94</t>
+    <t>N2_S0_E94_A1</t>
+  </si>
+  <si>
+    <t>N2_S0_E94_A2</t>
   </si>
   <si>
     <t>1F IDC机房热通道13#温湿度</t>
   </si>
   <si>
-    <t>N2_S0_E93</t>
+    <t>N2_S0_E93_A1</t>
+  </si>
+  <si>
+    <t>N2_S0_E93_A2</t>
   </si>
   <si>
     <t>1F IDC机房冷通道12#温湿度</t>
   </si>
   <si>
-    <t>N2_S0_E92</t>
+    <t>N2_S0_E92_A1</t>
+  </si>
+  <si>
+    <t>N2_S0_E92_A2</t>
   </si>
   <si>
     <t>1F IDC机房冷通道11#温湿度</t>
   </si>
   <si>
-    <t>N2_S0_E91</t>
+    <t>N2_S0_E91_A1</t>
+  </si>
+  <si>
+    <t>N2_S0_E91_A2</t>
   </si>
   <si>
     <t>1F IDC机房热通道10#温湿度</t>
   </si>
   <si>
-    <t>N2_S0_E90</t>
+    <t>N2_S0_E90_A1</t>
+  </si>
+  <si>
+    <t>N2_S0_E90_A2</t>
   </si>
   <si>
     <t>1F IDC机房热通道9#温湿度</t>
   </si>
   <si>
-    <t>N2_S0_E89</t>
+    <t>N2_S0_E89_A1</t>
+  </si>
+  <si>
+    <t>N2_S0_E89_A2</t>
   </si>
   <si>
     <t>1F IDC机房冷通道8#温湿度</t>
   </si>
   <si>
-    <t>N2_S0_E88</t>
+    <t>N2_S0_E88_A1</t>
+  </si>
+  <si>
+    <t>N2_S0_E88_A2</t>
   </si>
   <si>
     <t>1F IDC机房冷通道7#温湿度</t>
   </si>
   <si>
-    <t>N2_S0_E87</t>
+    <t>N2_S0_E87_A1</t>
+  </si>
+  <si>
+    <t>N2_S0_E87_A2</t>
   </si>
   <si>
     <t>1F IDC机房热通道6#温湿度</t>
   </si>
   <si>
-    <t>N2_S0_E86</t>
+    <t>N2_S0_E86_A1</t>
+  </si>
+  <si>
+    <t>N2_S0_E86_A2</t>
   </si>
   <si>
     <t>1F IDC机房热通道5#温湿度</t>
   </si>
   <si>
-    <t>N2_S0_E85</t>
+    <t>N2_S0_E85_A1</t>
+  </si>
+  <si>
+    <t>N2_S0_E85_A2</t>
   </si>
   <si>
     <t>1F IDC机房冷通道4#温湿度</t>
   </si>
   <si>
-    <t>N2_S0_E84</t>
+    <t>N2_S0_E84_A1</t>
+  </si>
+  <si>
+    <t>N2_S0_E84_A2</t>
   </si>
   <si>
     <t>1F IDC机房冷通道3#温湿度</t>
   </si>
   <si>
-    <t>N2_S0_E83</t>
+    <t>N2_S0_E83_A1</t>
+  </si>
+  <si>
+    <t>N2_S0_E83_A2</t>
   </si>
   <si>
     <t>1F IDC机房热通道2#温湿度</t>
   </si>
   <si>
-    <t>N2_S0_E82</t>
+    <t>N2_S0_E82_A1</t>
+  </si>
+  <si>
+    <t>N2_S0_E82_A2</t>
   </si>
   <si>
     <t>1F IDC机房热通道1#温湿度</t>
   </si>
   <si>
-    <t>N2_S0_E81</t>
-  </si>
-  <si>
-    <t>103A机房E列头柜B路</t>
-  </si>
-  <si>
-    <t>N2_S0_E40</t>
-  </si>
-  <si>
-    <t>103A机房F列头柜A路</t>
-  </si>
-  <si>
-    <t>N2_S0_E39</t>
-  </si>
-  <si>
-    <t>103A机房D列头柜B路</t>
-  </si>
-  <si>
-    <t>N2_S0_E38</t>
-  </si>
-  <si>
-    <t>103A机房D列头柜A路</t>
-  </si>
-  <si>
-    <t>N2_S0_E37</t>
-  </si>
-  <si>
-    <t>103A机房C列头柜B路</t>
-  </si>
-  <si>
-    <t>N2_S0_E36</t>
-  </si>
-  <si>
-    <t>103A机房C列头柜A路</t>
-  </si>
-  <si>
-    <t>N2_S0_E35</t>
-  </si>
-  <si>
-    <t>103A机房B列头柜B路</t>
-  </si>
-  <si>
-    <t>N2_S0_E34</t>
-  </si>
-  <si>
-    <t>103A机房B列头柜A路</t>
-  </si>
-  <si>
-    <t>N2_S0_E33</t>
-  </si>
-  <si>
-    <t>103A机房A列头柜B路</t>
-  </si>
-  <si>
-    <t>N2_S0_E32</t>
-  </si>
-  <si>
-    <t>103A机房A列头柜A路</t>
-  </si>
-  <si>
-    <t>N2_S0_E31</t>
-  </si>
-  <si>
-    <t>1F IDC机房1#空调</t>
-  </si>
-  <si>
-    <t>回风湿度设定点（%）</t>
-  </si>
-  <si>
-    <t>N2_S0_E1_A27</t>
-  </si>
-  <si>
-    <t>回风温度设定点（℃）</t>
-  </si>
-  <si>
-    <t>N2_S0_E1_A28</t>
-  </si>
-  <si>
-    <t>远程平均温度设定点（℃）</t>
-  </si>
-  <si>
-    <t>N2_S0_E1_A30</t>
-  </si>
-  <si>
-    <t>远程最高温度设定点（℃）</t>
-  </si>
-  <si>
-    <t>N2_S0_E1_A31</t>
-  </si>
-  <si>
-    <t>1F IDC机房2#空调</t>
-  </si>
-  <si>
-    <t>N2_S0_E2_A27</t>
-  </si>
-  <si>
-    <t>N2_S0_E2_A28</t>
-  </si>
-  <si>
-    <t>N2_S0_E2_A30</t>
-  </si>
-  <si>
-    <t>N2_S0_E2_A31</t>
-  </si>
-  <si>
-    <t>1F IDC机房3#空调</t>
-  </si>
-  <si>
-    <t>N2_S0_E3_A27</t>
-  </si>
-  <si>
-    <t>N2_S0_E3_A28</t>
-  </si>
-  <si>
-    <t>N2_S0_E3_A30</t>
-  </si>
-  <si>
-    <t>N2_S0_E3_A31</t>
-  </si>
-  <si>
-    <t>1F IDC机房4#空调</t>
-  </si>
-  <si>
-    <t>N2_S0_E4_A27</t>
-  </si>
-  <si>
-    <t>N2_S0_E4_A28</t>
-  </si>
-  <si>
-    <t>N2_S0_E4_A30</t>
-  </si>
-  <si>
-    <t>N2_S0_E4_A31</t>
-  </si>
-  <si>
-    <t>1F IDC机房5#空调</t>
-  </si>
-  <si>
-    <t>N2_S0_E5_A27</t>
-  </si>
-  <si>
-    <t>N2_S0_E5_A28</t>
-  </si>
-  <si>
-    <t>N2_S0_E5_A30</t>
-  </si>
-  <si>
-    <t>N2_S0_E5_A31</t>
-  </si>
-  <si>
-    <t>1F IDC机房6#空调</t>
-  </si>
-  <si>
-    <t>N2_S0_E6_A27</t>
-  </si>
-  <si>
-    <t>N2_S0_E6_A28</t>
-  </si>
-  <si>
-    <t>N2_S0_E6_A30</t>
-  </si>
-  <si>
-    <t>N2_S0_E6_A31</t>
-  </si>
-  <si>
-    <t>1F IDC机房7#空调</t>
-  </si>
-  <si>
-    <t>N2_S0_E7_A27</t>
-  </si>
-  <si>
-    <t>N2_S0_E7_A28</t>
-  </si>
-  <si>
-    <t>N2_S0_E7_A30</t>
-  </si>
-  <si>
-    <t>N2_S0_E7_A31</t>
-  </si>
-  <si>
-    <t>1F IDC机房8#空调</t>
-  </si>
-  <si>
-    <t>N2_S0_E8_A27</t>
-  </si>
-  <si>
-    <t>N2_S0_E8_A28</t>
-  </si>
-  <si>
-    <t>N2_S0_E8_A30</t>
-  </si>
-  <si>
-    <t>N2_S0_E8_A31</t>
-  </si>
-  <si>
-    <t>1F IDC机房9#空调</t>
-  </si>
-  <si>
-    <t>N2_S0_E9_A27</t>
-  </si>
-  <si>
-    <t>N2_S0_E9_A28</t>
-  </si>
-  <si>
-    <t>N2_S0_E9_A30</t>
-  </si>
-  <si>
-    <t>N2_S0_E9_A31</t>
+    <t>N2_S0_E81_A1</t>
+  </si>
+  <si>
+    <t>N2_S0_E81_A2</t>
   </si>
 </sst>
 </file>
@@ -510,14 +624,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
-    <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="21">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -677,12 +784,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8F8F8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -980,28 +1093,31 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1010,124 +1126,130 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1511,12 +1633,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="B1:D90"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="3"/>
+  <dimension ref="A1:AP125"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="26.0833333333333" customWidth="1"/>
     <col min="3" max="3" width="41.4166666666667" customWidth="1"/>
     <col min="6" max="6" width="35.3333333333333" customWidth="1"/>
+    <col min="22" max="22" width="70.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:3">
@@ -1687,671 +1810,3683 @@
         <v>41</v>
       </c>
     </row>
-    <row r="22" spans="2:3">
-      <c r="B22" t="s">
+    <row r="22" spans="2:4">
+      <c r="B22" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="C22" t="s">
+      <c r="C22" s="1" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="23" spans="2:3">
-      <c r="B23" t="s">
+      <c r="D22" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C23" t="s">
+    </row>
+    <row r="23" spans="2:4">
+      <c r="B23" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C23" s="1" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="24" spans="2:3">
-      <c r="B24" t="s">
+      <c r="D23" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C24" t="s">
+    </row>
+    <row r="24" spans="2:4">
+      <c r="B24" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C24" s="1" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="25" spans="2:3">
-      <c r="B25" t="s">
+      <c r="D24" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="C25" t="s">
+    </row>
+    <row r="25" spans="2:4">
+      <c r="B25" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C25" s="1" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="26" spans="2:3">
-      <c r="B26" t="s">
+      <c r="D25" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="C26" t="s">
+    </row>
+    <row r="26" spans="2:4">
+      <c r="B26" s="1" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="27" spans="2:3">
-      <c r="B27" t="s">
+      <c r="C26" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D26" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="C27" t="s">
+    </row>
+    <row r="27" spans="2:4">
+      <c r="B27" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D27" s="1" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="28" spans="2:3">
-      <c r="B28" t="s">
+    <row r="28" spans="2:4">
+      <c r="B28" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D28" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="C28" t="s">
+    </row>
+    <row r="29" spans="2:4">
+      <c r="B29" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D29" s="1" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="29" spans="2:3">
-      <c r="B29" t="s">
+    <row r="30" spans="2:4">
+      <c r="B30" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="C29" t="s">
+      <c r="C30" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D30" s="1" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="30" spans="2:3">
-      <c r="B30" t="s">
+    <row r="31" spans="2:4">
+      <c r="B31" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D31" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="C30" t="s">
+    </row>
+    <row r="32" spans="2:4">
+      <c r="B32" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D32" s="1" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="31" spans="2:3">
-      <c r="B31" t="s">
+    <row r="33" spans="2:4">
+      <c r="B33" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D33" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="C31" t="s">
+    </row>
+    <row r="34" spans="2:4">
+      <c r="B34" s="1" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="32" spans="2:3">
-      <c r="B32" t="s">
+      <c r="C34" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D34" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="C32" t="s">
+    </row>
+    <row r="35" spans="2:4">
+      <c r="B35" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D35" s="1" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="33" spans="2:3">
-      <c r="B33" t="s">
+    <row r="36" spans="2:4">
+      <c r="B36" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D36" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="C33" t="s">
+    </row>
+    <row r="37" spans="2:4">
+      <c r="B37" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D37" s="1" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="34" spans="2:3">
-      <c r="B34" t="s">
+    <row r="38" spans="2:4">
+      <c r="B38" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="C34" t="s">
+      <c r="C38" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D38" s="1" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="35" spans="2:3">
-      <c r="B35" t="s">
+    <row r="39" spans="2:4">
+      <c r="B39" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D39" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="C35" t="s">
+    </row>
+    <row r="40" spans="2:4">
+      <c r="B40" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D40" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="36" spans="2:3">
-      <c r="B36" t="s">
+    <row r="41" spans="2:4">
+      <c r="B41" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D41" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="C36" t="s">
+    </row>
+    <row r="42" spans="2:4">
+      <c r="B42" s="1" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="37" spans="2:3">
-      <c r="B37" t="s">
+      <c r="C42" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D42" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="C37" t="s">
+    </row>
+    <row r="43" spans="2:4">
+      <c r="B43" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D43" s="1" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="38" spans="2:3">
-      <c r="B38" t="s">
+    <row r="44" spans="2:4">
+      <c r="B44" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D44" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="C38" t="s">
+    </row>
+    <row r="45" spans="2:4">
+      <c r="B45" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D45" s="1" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="39" spans="2:3">
-      <c r="B39" t="s">
+    <row r="46" spans="2:4">
+      <c r="B46" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="C39" t="s">
+      <c r="C46" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D46" s="1" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="40" spans="2:3">
-      <c r="B40" t="s">
+    <row r="47" spans="2:4">
+      <c r="B47" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D47" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="C40" t="s">
+    </row>
+    <row r="48" spans="2:4">
+      <c r="B48" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D48" s="1" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="41" spans="2:3">
-      <c r="B41" t="s">
+    <row r="49" spans="2:4">
+      <c r="B49" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D49" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="C41" t="s">
+    </row>
+    <row r="50" spans="2:4">
+      <c r="B50" s="1" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="42" spans="2:3">
-      <c r="B42" t="s">
+      <c r="C50" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D50" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="C42" t="s">
+    </row>
+    <row r="51" spans="2:4">
+      <c r="B51" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D51" s="1" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="43" spans="2:3">
-      <c r="B43" t="s">
+    <row r="52" spans="2:4">
+      <c r="B52" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D52" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="C43" t="s">
+    </row>
+    <row r="53" spans="2:4">
+      <c r="B53" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D53" s="1" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="44" spans="2:3">
-      <c r="B44" t="s">
+    <row r="54" spans="2:4">
+      <c r="B54" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="C44" t="s">
+      <c r="C54" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D54" s="1" t="s">
         <v>87</v>
-      </c>
-    </row>
-    <row r="45" spans="2:3">
-      <c r="B45" t="s">
-        <v>88</v>
-      </c>
-      <c r="C45" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="46" spans="2:3">
-      <c r="B46" t="s">
-        <v>90</v>
-      </c>
-      <c r="C46" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="47" spans="2:3">
-      <c r="B47" t="s">
-        <v>92</v>
-      </c>
-      <c r="C47" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="48" spans="2:3">
-      <c r="B48" t="s">
-        <v>94</v>
-      </c>
-      <c r="C48" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="49" spans="2:3">
-      <c r="B49" t="s">
-        <v>96</v>
-      </c>
-      <c r="C49" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="50" spans="2:3">
-      <c r="B50" t="s">
-        <v>98</v>
-      </c>
-      <c r="C50" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="51" spans="2:3">
-      <c r="B51" t="s">
-        <v>100</v>
-      </c>
-      <c r="C51" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="52" spans="2:3">
-      <c r="B52" t="s">
-        <v>102</v>
-      </c>
-      <c r="C52" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="53" spans="2:3">
-      <c r="B53" t="s">
-        <v>104</v>
-      </c>
-      <c r="C53" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="54" spans="2:3">
-      <c r="B54" t="s">
-        <v>106</v>
-      </c>
-      <c r="C54" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="55" spans="2:4">
       <c r="B55" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="56" spans="2:37">
+      <c r="B56" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="AJ56" s="3"/>
+      <c r="AK56" s="3"/>
+    </row>
+    <row r="57" spans="2:37">
+      <c r="B57" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="AJ57" s="3"/>
+      <c r="AK57" s="3"/>
+    </row>
+    <row r="58" spans="1:42">
+      <c r="A58" s="2"/>
+      <c r="B58" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="C58" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="D58" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="E58" s="4"/>
+      <c r="F58" s="4"/>
+      <c r="G58" s="4"/>
+      <c r="H58" s="4"/>
+      <c r="I58" s="4"/>
+      <c r="J58" s="3"/>
+      <c r="K58" s="4"/>
+      <c r="L58" s="4"/>
+      <c r="M58" s="4"/>
+      <c r="N58" s="4"/>
+      <c r="O58"/>
+      <c r="P58"/>
+      <c r="Q58"/>
+      <c r="R58"/>
+      <c r="T58" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="U58" s="4"/>
+      <c r="W58" s="4"/>
+      <c r="X58" s="4"/>
+      <c r="Y58" s="4"/>
+      <c r="Z58" s="3"/>
+      <c r="AA58" s="3"/>
+      <c r="AB58" s="3"/>
+      <c r="AC58" s="3"/>
+      <c r="AD58" s="3"/>
+      <c r="AE58" s="3"/>
+      <c r="AF58" s="3"/>
+      <c r="AG58" s="3"/>
+      <c r="AH58" s="3"/>
+      <c r="AI58" s="3"/>
+      <c r="AJ58" s="3"/>
+      <c r="AK58" s="3"/>
+      <c r="AL58" s="3"/>
+      <c r="AM58" s="3"/>
+      <c r="AN58" s="3"/>
+      <c r="AO58" s="3"/>
+      <c r="AP58" s="3"/>
+    </row>
+    <row r="59" spans="1:42">
+      <c r="A59" s="2"/>
+      <c r="B59" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="C59" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="D59" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="E59" s="4"/>
+      <c r="F59" s="4"/>
+      <c r="G59" s="4"/>
+      <c r="H59" s="4"/>
+      <c r="I59" s="4"/>
+      <c r="J59" s="3"/>
+      <c r="K59" s="4"/>
+      <c r="L59" s="4"/>
+      <c r="M59" s="4"/>
+      <c r="N59" s="4"/>
+      <c r="O59"/>
+      <c r="P59"/>
+      <c r="Q59"/>
+      <c r="R59"/>
+      <c r="T59" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="U59" s="4"/>
+      <c r="W59" s="4"/>
+      <c r="X59" s="4"/>
+      <c r="Y59" s="4"/>
+      <c r="Z59" s="3"/>
+      <c r="AA59" s="3"/>
+      <c r="AB59" s="3"/>
+      <c r="AC59" s="3"/>
+      <c r="AD59" s="3"/>
+      <c r="AE59" s="3"/>
+      <c r="AF59" s="3"/>
+      <c r="AG59" s="3"/>
+      <c r="AH59" s="3"/>
+      <c r="AI59" s="3"/>
+      <c r="AJ59" s="3"/>
+      <c r="AK59" s="3"/>
+      <c r="AL59" s="3"/>
+      <c r="AM59" s="3"/>
+      <c r="AN59" s="3"/>
+      <c r="AO59" s="3"/>
+      <c r="AP59" s="3"/>
+    </row>
+    <row r="60" spans="1:42">
+      <c r="A60" s="2"/>
+      <c r="B60" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="C60" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="D60" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="E60" s="4"/>
+      <c r="F60" s="4"/>
+      <c r="G60" s="4"/>
+      <c r="H60" s="4"/>
+      <c r="I60" s="4"/>
+      <c r="J60" s="3"/>
+      <c r="K60" s="4"/>
+      <c r="L60" s="4"/>
+      <c r="M60" s="4"/>
+      <c r="N60" s="4"/>
+      <c r="O60"/>
+      <c r="P60"/>
+      <c r="Q60"/>
+      <c r="R60"/>
+      <c r="T60" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="U60" s="4"/>
+      <c r="W60" s="4"/>
+      <c r="X60" s="4"/>
+      <c r="Y60" s="4"/>
+      <c r="Z60" s="3"/>
+      <c r="AA60" s="3"/>
+      <c r="AB60" s="3"/>
+      <c r="AC60" s="3"/>
+      <c r="AD60" s="3"/>
+      <c r="AE60" s="3"/>
+      <c r="AF60" s="3"/>
+      <c r="AG60" s="3"/>
+      <c r="AH60" s="3"/>
+      <c r="AI60" s="3"/>
+      <c r="AJ60" s="3"/>
+      <c r="AK60" s="3"/>
+      <c r="AL60" s="3"/>
+      <c r="AM60" s="3"/>
+      <c r="AN60" s="3"/>
+      <c r="AO60" s="3"/>
+      <c r="AP60" s="3"/>
+    </row>
+    <row r="61" spans="1:42">
+      <c r="A61" s="2"/>
+      <c r="B61" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="C61" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="D61" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="E61" s="4"/>
+      <c r="F61" s="4"/>
+      <c r="G61" s="4"/>
+      <c r="H61" s="4"/>
+      <c r="I61" s="4"/>
+      <c r="J61" s="3"/>
+      <c r="K61" s="4"/>
+      <c r="L61" s="4"/>
+      <c r="M61" s="4"/>
+      <c r="N61" s="4"/>
+      <c r="O61"/>
+      <c r="P61"/>
+      <c r="Q61"/>
+      <c r="R61"/>
+      <c r="T61" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="U61" s="4"/>
+      <c r="W61" s="4"/>
+      <c r="X61" s="4"/>
+      <c r="Y61" s="4"/>
+      <c r="Z61" s="3"/>
+      <c r="AA61" s="3"/>
+      <c r="AB61" s="3"/>
+      <c r="AC61" s="3"/>
+      <c r="AD61" s="3"/>
+      <c r="AE61" s="3"/>
+      <c r="AF61" s="3"/>
+      <c r="AG61" s="3"/>
+      <c r="AH61" s="3"/>
+      <c r="AI61" s="3"/>
+      <c r="AJ61" s="3"/>
+      <c r="AK61" s="3"/>
+      <c r="AL61" s="3"/>
+      <c r="AM61" s="3"/>
+      <c r="AN61" s="3"/>
+      <c r="AO61" s="3"/>
+      <c r="AP61" s="3"/>
+    </row>
+    <row r="62" spans="1:42">
+      <c r="A62" s="2"/>
+      <c r="B62" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="C62" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="D62" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="E62" s="4"/>
+      <c r="F62" s="4"/>
+      <c r="G62" s="4"/>
+      <c r="H62" s="4"/>
+      <c r="I62" s="4"/>
+      <c r="J62" s="3"/>
+      <c r="K62" s="4"/>
+      <c r="L62" s="4"/>
+      <c r="M62" s="4"/>
+      <c r="N62" s="4"/>
+      <c r="O62"/>
+      <c r="P62"/>
+      <c r="Q62"/>
+      <c r="R62"/>
+      <c r="T62" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="U62" s="4"/>
+      <c r="W62" s="4"/>
+      <c r="X62" s="4"/>
+      <c r="Y62" s="4"/>
+      <c r="Z62" s="3"/>
+      <c r="AA62" s="3"/>
+      <c r="AB62" s="3"/>
+      <c r="AC62" s="3"/>
+      <c r="AD62" s="3"/>
+      <c r="AE62" s="3"/>
+      <c r="AF62" s="3"/>
+      <c r="AG62" s="3"/>
+      <c r="AH62" s="3"/>
+      <c r="AI62" s="3"/>
+      <c r="AJ62" s="3"/>
+      <c r="AK62" s="3"/>
+      <c r="AL62" s="3"/>
+      <c r="AM62" s="3"/>
+      <c r="AN62" s="3"/>
+      <c r="AO62" s="3"/>
+      <c r="AP62" s="3"/>
+    </row>
+    <row r="63" spans="1:42">
+      <c r="A63" s="2"/>
+      <c r="B63" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="C63" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="D63" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="E63" s="4"/>
+      <c r="F63" s="4"/>
+      <c r="G63" s="4"/>
+      <c r="H63" s="4"/>
+      <c r="I63" s="4"/>
+      <c r="J63" s="3"/>
+      <c r="K63" s="4"/>
+      <c r="L63" s="4"/>
+      <c r="M63" s="4"/>
+      <c r="N63" s="4"/>
+      <c r="O63"/>
+      <c r="P63"/>
+      <c r="Q63"/>
+      <c r="R63"/>
+      <c r="T63" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="U63" s="4"/>
+      <c r="W63" s="4"/>
+      <c r="X63" s="4"/>
+      <c r="Y63" s="4"/>
+      <c r="Z63" s="3"/>
+      <c r="AA63" s="3"/>
+      <c r="AB63" s="3"/>
+      <c r="AC63" s="3"/>
+      <c r="AD63" s="3"/>
+      <c r="AE63" s="3"/>
+      <c r="AF63" s="3"/>
+      <c r="AG63" s="3"/>
+      <c r="AH63" s="3"/>
+      <c r="AI63" s="3"/>
+      <c r="AJ63" s="3"/>
+      <c r="AK63" s="3"/>
+      <c r="AL63" s="3"/>
+      <c r="AM63" s="3"/>
+      <c r="AN63" s="3"/>
+      <c r="AO63" s="3"/>
+      <c r="AP63" s="3"/>
+    </row>
+    <row r="64" spans="1:42">
+      <c r="A64" s="2"/>
+      <c r="B64" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="C64" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="D64" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="E64" s="4"/>
+      <c r="F64" s="4"/>
+      <c r="G64" s="4"/>
+      <c r="H64" s="4"/>
+      <c r="I64" s="4"/>
+      <c r="J64" s="3"/>
+      <c r="K64" s="4"/>
+      <c r="L64" s="4"/>
+      <c r="M64" s="4"/>
+      <c r="N64" s="4"/>
+      <c r="O64"/>
+      <c r="P64"/>
+      <c r="Q64"/>
+      <c r="R64"/>
+      <c r="T64" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="U64" s="4"/>
+      <c r="W64" s="4"/>
+      <c r="X64" s="4"/>
+      <c r="Y64" s="4"/>
+      <c r="Z64" s="3"/>
+      <c r="AA64" s="3"/>
+      <c r="AB64" s="3"/>
+      <c r="AC64" s="3"/>
+      <c r="AD64" s="3"/>
+      <c r="AE64" s="3"/>
+      <c r="AF64" s="3"/>
+      <c r="AG64" s="3"/>
+      <c r="AH64" s="3"/>
+      <c r="AI64" s="3"/>
+      <c r="AJ64" s="3"/>
+      <c r="AK64" s="3"/>
+      <c r="AL64" s="3"/>
+      <c r="AM64" s="3"/>
+      <c r="AN64" s="3"/>
+      <c r="AO64" s="3"/>
+      <c r="AP64" s="3"/>
+    </row>
+    <row r="65" spans="1:42">
+      <c r="A65" s="2"/>
+      <c r="B65" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="C65" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="D65" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="E65" s="4"/>
+      <c r="F65" s="4"/>
+      <c r="G65" s="4"/>
+      <c r="H65" s="4"/>
+      <c r="I65" s="4"/>
+      <c r="J65" s="3"/>
+      <c r="K65" s="4"/>
+      <c r="L65" s="4"/>
+      <c r="M65" s="4"/>
+      <c r="N65" s="4"/>
+      <c r="O65"/>
+      <c r="P65"/>
+      <c r="Q65"/>
+      <c r="R65"/>
+      <c r="T65" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="U65" s="4"/>
+      <c r="W65" s="4"/>
+      <c r="X65" s="4"/>
+      <c r="Y65" s="4"/>
+      <c r="Z65" s="3"/>
+      <c r="AA65" s="3"/>
+      <c r="AB65" s="3"/>
+      <c r="AC65" s="3"/>
+      <c r="AD65" s="3"/>
+      <c r="AE65" s="3"/>
+      <c r="AF65" s="3"/>
+      <c r="AG65" s="3"/>
+      <c r="AH65" s="3"/>
+      <c r="AI65" s="3"/>
+      <c r="AJ65" s="3"/>
+      <c r="AK65" s="3"/>
+      <c r="AL65" s="3"/>
+      <c r="AM65" s="3"/>
+      <c r="AN65" s="3"/>
+      <c r="AO65" s="3"/>
+      <c r="AP65" s="3"/>
+    </row>
+    <row r="66" spans="1:42">
+      <c r="A66" s="2"/>
+      <c r="B66" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="C66" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="D66" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="E66" s="4"/>
+      <c r="F66" s="4"/>
+      <c r="G66" s="4"/>
+      <c r="H66" s="4"/>
+      <c r="I66" s="4"/>
+      <c r="J66" s="3"/>
+      <c r="K66" s="4"/>
+      <c r="L66" s="4"/>
+      <c r="M66" s="4"/>
+      <c r="N66" s="4"/>
+      <c r="O66"/>
+      <c r="P66"/>
+      <c r="Q66"/>
+      <c r="R66"/>
+      <c r="T66" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="U66" s="4"/>
+      <c r="W66" s="4"/>
+      <c r="X66" s="4"/>
+      <c r="Y66" s="4"/>
+      <c r="Z66" s="3"/>
+      <c r="AA66" s="3"/>
+      <c r="AB66" s="3"/>
+      <c r="AC66" s="3"/>
+      <c r="AD66" s="3"/>
+      <c r="AE66" s="3"/>
+      <c r="AF66" s="3"/>
+      <c r="AG66" s="3"/>
+      <c r="AH66" s="3"/>
+      <c r="AI66" s="3"/>
+      <c r="AJ66" s="3"/>
+      <c r="AK66" s="3"/>
+      <c r="AL66" s="3"/>
+      <c r="AM66" s="3"/>
+      <c r="AN66" s="3"/>
+      <c r="AO66" s="3"/>
+      <c r="AP66" s="3"/>
+    </row>
+    <row r="67" spans="1:42">
+      <c r="A67" s="2"/>
+      <c r="B67" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="C67" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="D67" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="C55" s="1" t="s">
+      <c r="E67" s="4"/>
+      <c r="F67" s="4"/>
+      <c r="G67" s="4"/>
+      <c r="H67" s="4"/>
+      <c r="I67" s="4"/>
+      <c r="J67" s="3"/>
+      <c r="K67" s="4"/>
+      <c r="L67" s="4"/>
+      <c r="M67" s="4"/>
+      <c r="N67" s="4"/>
+      <c r="O67"/>
+      <c r="P67"/>
+      <c r="Q67"/>
+      <c r="R67"/>
+      <c r="T67" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="U67" s="4"/>
+      <c r="W67" s="4"/>
+      <c r="X67" s="4"/>
+      <c r="Y67" s="4"/>
+      <c r="Z67" s="3"/>
+      <c r="AA67" s="3"/>
+      <c r="AB67" s="3"/>
+      <c r="AC67" s="3"/>
+      <c r="AD67" s="3"/>
+      <c r="AE67" s="3"/>
+      <c r="AF67" s="3"/>
+      <c r="AG67" s="3"/>
+      <c r="AH67" s="3"/>
+      <c r="AI67" s="3"/>
+      <c r="AJ67" s="3"/>
+      <c r="AK67" s="3"/>
+      <c r="AL67" s="3"/>
+      <c r="AM67" s="3"/>
+      <c r="AN67" s="3"/>
+      <c r="AO67" s="3"/>
+      <c r="AP67" s="3"/>
+    </row>
+    <row r="68" spans="1:42">
+      <c r="A68" s="2"/>
+      <c r="B68" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="D55" s="1" t="s">
+      <c r="C68" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="D68" s="4" t="s">
         <v>110</v>
       </c>
-    </row>
-    <row r="56" spans="2:4">
-      <c r="B56" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="C56" s="1" t="s">
+      <c r="E68" s="4"/>
+      <c r="F68" s="4"/>
+      <c r="G68" s="4"/>
+      <c r="H68" s="4"/>
+      <c r="I68" s="4"/>
+      <c r="J68" s="3"/>
+      <c r="K68" s="4"/>
+      <c r="L68" s="4"/>
+      <c r="M68" s="4"/>
+      <c r="N68" s="4"/>
+      <c r="O68"/>
+      <c r="P68"/>
+      <c r="Q68"/>
+      <c r="R68"/>
+      <c r="T68" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="U68" s="4"/>
+      <c r="W68" s="4"/>
+      <c r="X68" s="4"/>
+      <c r="Y68" s="4"/>
+      <c r="Z68" s="3"/>
+      <c r="AA68" s="3"/>
+      <c r="AB68" s="3"/>
+      <c r="AC68" s="3"/>
+      <c r="AD68" s="3"/>
+      <c r="AE68" s="3"/>
+      <c r="AF68" s="3"/>
+      <c r="AG68" s="3"/>
+      <c r="AH68" s="3"/>
+      <c r="AI68" s="3"/>
+      <c r="AJ68" s="3"/>
+      <c r="AK68" s="3"/>
+      <c r="AL68" s="3"/>
+      <c r="AM68" s="3"/>
+      <c r="AN68" s="3"/>
+      <c r="AO68" s="3"/>
+      <c r="AP68" s="3"/>
+    </row>
+    <row r="69" spans="1:42">
+      <c r="A69" s="2"/>
+      <c r="B69" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="C69" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="D69" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="D56" s="1" t="s">
+      <c r="E69" s="4"/>
+      <c r="F69" s="4"/>
+      <c r="G69" s="4"/>
+      <c r="H69" s="4"/>
+      <c r="I69" s="4"/>
+      <c r="J69" s="3"/>
+      <c r="K69" s="4"/>
+      <c r="L69" s="4"/>
+      <c r="M69" s="4"/>
+      <c r="N69" s="4"/>
+      <c r="O69"/>
+      <c r="P69"/>
+      <c r="Q69"/>
+      <c r="R69"/>
+      <c r="T69" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="U69" s="4"/>
+      <c r="W69" s="4"/>
+      <c r="X69" s="4"/>
+      <c r="Y69" s="4"/>
+      <c r="Z69" s="3"/>
+      <c r="AA69" s="3"/>
+      <c r="AB69" s="3"/>
+      <c r="AC69" s="3"/>
+      <c r="AD69" s="3"/>
+      <c r="AE69" s="3"/>
+      <c r="AF69" s="3"/>
+      <c r="AG69" s="3"/>
+      <c r="AH69" s="3"/>
+      <c r="AI69" s="3"/>
+      <c r="AJ69" s="3"/>
+      <c r="AK69" s="3"/>
+      <c r="AL69" s="3"/>
+      <c r="AM69" s="3"/>
+      <c r="AN69" s="3"/>
+      <c r="AO69" s="3"/>
+      <c r="AP69" s="3"/>
+    </row>
+    <row r="70" spans="1:42">
+      <c r="A70" s="2"/>
+      <c r="B70" s="3" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="57" spans="2:4">
-      <c r="B57" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="C57" s="1" t="s">
+      <c r="C70" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="D70" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="D57" s="1" t="s">
+      <c r="E70" s="4"/>
+      <c r="F70" s="4"/>
+      <c r="G70" s="4"/>
+      <c r="H70" s="4"/>
+      <c r="I70" s="4"/>
+      <c r="J70" s="3"/>
+      <c r="K70" s="4"/>
+      <c r="L70" s="4"/>
+      <c r="M70" s="4"/>
+      <c r="N70" s="4"/>
+      <c r="O70"/>
+      <c r="P70"/>
+      <c r="Q70"/>
+      <c r="R70"/>
+      <c r="T70" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="U70" s="4"/>
+      <c r="W70" s="4"/>
+      <c r="X70" s="4"/>
+      <c r="Y70" s="4"/>
+      <c r="Z70" s="3"/>
+      <c r="AA70" s="3"/>
+      <c r="AB70" s="3"/>
+      <c r="AC70" s="3"/>
+      <c r="AD70" s="3"/>
+      <c r="AE70" s="3"/>
+      <c r="AF70" s="3"/>
+      <c r="AG70" s="3"/>
+      <c r="AH70" s="3"/>
+      <c r="AI70" s="3"/>
+      <c r="AJ70" s="3"/>
+      <c r="AK70" s="3"/>
+      <c r="AL70" s="3"/>
+      <c r="AM70" s="3"/>
+      <c r="AN70" s="3"/>
+      <c r="AO70" s="3"/>
+      <c r="AP70" s="3"/>
+    </row>
+    <row r="71" spans="1:42">
+      <c r="A71" s="2"/>
+      <c r="B71" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="C71" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="D71" s="4" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="58" spans="2:4">
-      <c r="B58" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="C58" s="1" t="s">
+      <c r="E71" s="4"/>
+      <c r="F71" s="4"/>
+      <c r="G71" s="4"/>
+      <c r="H71" s="4"/>
+      <c r="I71" s="4"/>
+      <c r="J71" s="3"/>
+      <c r="K71" s="4"/>
+      <c r="L71" s="4"/>
+      <c r="M71" s="4"/>
+      <c r="N71" s="4"/>
+      <c r="O71"/>
+      <c r="P71"/>
+      <c r="Q71"/>
+      <c r="R71"/>
+      <c r="T71" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="U71" s="4"/>
+      <c r="W71" s="4"/>
+      <c r="X71" s="4"/>
+      <c r="Y71" s="4"/>
+      <c r="Z71" s="3"/>
+      <c r="AA71" s="3"/>
+      <c r="AB71" s="3"/>
+      <c r="AC71" s="3"/>
+      <c r="AD71" s="3"/>
+      <c r="AE71" s="3"/>
+      <c r="AF71" s="3"/>
+      <c r="AG71" s="3"/>
+      <c r="AH71" s="3"/>
+      <c r="AI71" s="3"/>
+      <c r="AJ71" s="3"/>
+      <c r="AK71" s="3"/>
+      <c r="AL71" s="3"/>
+      <c r="AM71" s="3"/>
+      <c r="AN71" s="3"/>
+      <c r="AO71" s="3"/>
+      <c r="AP71" s="3"/>
+    </row>
+    <row r="72" spans="1:42">
+      <c r="A72" s="2"/>
+      <c r="B72" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="D58" s="1" t="s">
+      <c r="C72" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="D72" s="4" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="59" spans="2:4">
-      <c r="B59" s="1" t="s">
+      <c r="E72" s="4"/>
+      <c r="F72" s="4"/>
+      <c r="G72" s="4"/>
+      <c r="H72" s="4"/>
+      <c r="I72" s="4"/>
+      <c r="J72" s="3"/>
+      <c r="K72" s="4"/>
+      <c r="L72" s="4"/>
+      <c r="M72" s="4"/>
+      <c r="N72" s="4"/>
+      <c r="O72"/>
+      <c r="P72"/>
+      <c r="Q72"/>
+      <c r="R72"/>
+      <c r="T72" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="U72" s="4"/>
+      <c r="W72" s="4"/>
+      <c r="X72" s="4"/>
+      <c r="Y72" s="4"/>
+      <c r="Z72" s="3"/>
+      <c r="AA72" s="3"/>
+      <c r="AB72" s="3"/>
+      <c r="AC72" s="3"/>
+      <c r="AD72" s="3"/>
+      <c r="AE72" s="3"/>
+      <c r="AF72" s="3"/>
+      <c r="AG72" s="3"/>
+      <c r="AH72" s="3"/>
+      <c r="AI72" s="3"/>
+      <c r="AJ72" s="3"/>
+      <c r="AK72" s="3"/>
+      <c r="AL72" s="3"/>
+      <c r="AM72" s="3"/>
+      <c r="AN72" s="3"/>
+      <c r="AO72" s="3"/>
+      <c r="AP72" s="3"/>
+    </row>
+    <row r="73" spans="1:42">
+      <c r="A73" s="2"/>
+      <c r="B73" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="C73" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="D73" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="C59" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="D59" s="1" t="s">
+      <c r="E73" s="4"/>
+      <c r="F73" s="4"/>
+      <c r="G73" s="4"/>
+      <c r="H73" s="4"/>
+      <c r="I73" s="4"/>
+      <c r="J73" s="3"/>
+      <c r="K73" s="4"/>
+      <c r="L73" s="4"/>
+      <c r="M73" s="4"/>
+      <c r="N73" s="4"/>
+      <c r="O73"/>
+      <c r="P73"/>
+      <c r="Q73"/>
+      <c r="R73"/>
+      <c r="T73" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="U73" s="4"/>
+      <c r="W73" s="4"/>
+      <c r="X73" s="4"/>
+      <c r="Y73" s="4"/>
+      <c r="Z73" s="3"/>
+      <c r="AA73" s="3"/>
+      <c r="AB73" s="3"/>
+      <c r="AC73" s="3"/>
+      <c r="AD73" s="3"/>
+      <c r="AE73" s="3"/>
+      <c r="AF73" s="3"/>
+      <c r="AG73" s="3"/>
+      <c r="AH73" s="3"/>
+      <c r="AI73" s="3"/>
+      <c r="AJ73" s="3"/>
+      <c r="AK73" s="3"/>
+      <c r="AL73" s="3"/>
+      <c r="AM73" s="3"/>
+      <c r="AN73" s="3"/>
+      <c r="AO73" s="3"/>
+      <c r="AP73" s="3"/>
+    </row>
+    <row r="74" spans="1:42">
+      <c r="A74" s="2"/>
+      <c r="B74" s="3" t="s">
         <v>118</v>
       </c>
-    </row>
-    <row r="60" spans="2:4">
-      <c r="B60" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="C60" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="D60" s="1" t="s">
+      <c r="C74" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="D74" s="4" t="s">
         <v>119</v>
       </c>
-    </row>
-    <row r="61" spans="2:4">
-      <c r="B61" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="C61" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="D61" s="1" t="s">
+      <c r="E74" s="4"/>
+      <c r="F74" s="4"/>
+      <c r="G74" s="4"/>
+      <c r="H74" s="4"/>
+      <c r="I74" s="4"/>
+      <c r="J74" s="3"/>
+      <c r="K74" s="4"/>
+      <c r="L74" s="4"/>
+      <c r="M74" s="4"/>
+      <c r="N74" s="4"/>
+      <c r="O74"/>
+      <c r="P74"/>
+      <c r="Q74"/>
+      <c r="R74"/>
+      <c r="T74" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="U74" s="4"/>
+      <c r="W74" s="4"/>
+      <c r="X74" s="4"/>
+      <c r="Y74" s="4"/>
+      <c r="Z74" s="3"/>
+      <c r="AA74" s="3"/>
+      <c r="AB74" s="3"/>
+      <c r="AC74" s="3"/>
+      <c r="AD74" s="3"/>
+      <c r="AE74" s="3"/>
+      <c r="AF74" s="3"/>
+      <c r="AG74" s="3"/>
+      <c r="AH74" s="3"/>
+      <c r="AI74" s="3"/>
+      <c r="AJ74" s="3"/>
+      <c r="AK74" s="3"/>
+      <c r="AL74" s="3"/>
+      <c r="AM74" s="3"/>
+      <c r="AN74" s="3"/>
+      <c r="AO74" s="3"/>
+      <c r="AP74" s="3"/>
+    </row>
+    <row r="75" spans="1:42">
+      <c r="A75" s="2"/>
+      <c r="B75" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="C75" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="D75" s="4" t="s">
         <v>120</v>
       </c>
-    </row>
-    <row r="62" spans="2:4">
-      <c r="B62" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="C62" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="D62" s="1" t="s">
+      <c r="E75" s="4"/>
+      <c r="F75" s="4"/>
+      <c r="G75" s="4"/>
+      <c r="H75" s="4"/>
+      <c r="I75" s="4"/>
+      <c r="J75" s="3"/>
+      <c r="K75" s="4"/>
+      <c r="L75" s="4"/>
+      <c r="M75" s="4"/>
+      <c r="N75" s="4"/>
+      <c r="O75"/>
+      <c r="P75"/>
+      <c r="Q75"/>
+      <c r="R75"/>
+      <c r="T75" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="U75" s="4"/>
+      <c r="W75" s="4"/>
+      <c r="X75" s="4"/>
+      <c r="Y75" s="4"/>
+      <c r="Z75" s="3"/>
+      <c r="AA75" s="3"/>
+      <c r="AB75" s="3"/>
+      <c r="AC75" s="3"/>
+      <c r="AD75" s="3"/>
+      <c r="AE75" s="3"/>
+      <c r="AF75" s="3"/>
+      <c r="AG75" s="3"/>
+      <c r="AH75" s="3"/>
+      <c r="AI75" s="3"/>
+      <c r="AJ75" s="3"/>
+      <c r="AK75" s="3"/>
+      <c r="AL75" s="3"/>
+      <c r="AM75" s="3"/>
+      <c r="AN75" s="3"/>
+      <c r="AO75" s="3"/>
+      <c r="AP75" s="3"/>
+    </row>
+    <row r="76" spans="1:42">
+      <c r="A76" s="2"/>
+      <c r="B76" s="3" t="s">
         <v>121</v>
       </c>
-    </row>
-    <row r="63" spans="2:4">
-      <c r="B63" s="1" t="s">
+      <c r="C76" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="D76" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="C63" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="D63" s="1" t="s">
+      <c r="E76" s="4"/>
+      <c r="F76" s="4"/>
+      <c r="G76" s="4"/>
+      <c r="H76" s="4"/>
+      <c r="I76" s="4"/>
+      <c r="J76" s="3"/>
+      <c r="K76" s="4"/>
+      <c r="L76" s="4"/>
+      <c r="M76" s="4"/>
+      <c r="N76" s="4"/>
+      <c r="O76"/>
+      <c r="P76"/>
+      <c r="Q76"/>
+      <c r="R76"/>
+      <c r="T76" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="U76" s="4"/>
+      <c r="W76" s="4"/>
+      <c r="X76" s="4"/>
+      <c r="Y76" s="4"/>
+      <c r="Z76" s="3"/>
+      <c r="AA76" s="3"/>
+      <c r="AB76" s="3"/>
+      <c r="AC76" s="3"/>
+      <c r="AD76" s="3"/>
+      <c r="AE76" s="3"/>
+      <c r="AF76" s="3"/>
+      <c r="AG76" s="3"/>
+      <c r="AH76" s="3"/>
+      <c r="AI76" s="3"/>
+      <c r="AJ76" s="3"/>
+      <c r="AK76" s="3"/>
+      <c r="AL76" s="3"/>
+      <c r="AM76" s="3"/>
+      <c r="AN76" s="3"/>
+      <c r="AO76" s="3"/>
+      <c r="AP76" s="3"/>
+    </row>
+    <row r="77" spans="1:42">
+      <c r="A77" s="2"/>
+      <c r="B77" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="C77" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="D77" s="4" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="64" spans="2:4">
-      <c r="B64" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="C64" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="D64" s="1" t="s">
+      <c r="E77" s="4"/>
+      <c r="F77" s="4"/>
+      <c r="G77" s="4"/>
+      <c r="H77" s="4"/>
+      <c r="I77" s="4"/>
+      <c r="J77" s="3"/>
+      <c r="K77" s="4"/>
+      <c r="L77" s="4"/>
+      <c r="M77" s="4"/>
+      <c r="N77" s="4"/>
+      <c r="O77"/>
+      <c r="P77"/>
+      <c r="Q77"/>
+      <c r="R77"/>
+      <c r="T77" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="U77" s="4"/>
+      <c r="W77" s="4"/>
+      <c r="X77" s="4"/>
+      <c r="Y77" s="4"/>
+      <c r="Z77" s="3"/>
+      <c r="AA77" s="3"/>
+      <c r="AB77" s="3"/>
+      <c r="AC77" s="3"/>
+      <c r="AD77" s="3"/>
+      <c r="AE77" s="3"/>
+      <c r="AF77" s="3"/>
+      <c r="AG77" s="3"/>
+      <c r="AH77" s="3"/>
+      <c r="AI77" s="3"/>
+      <c r="AJ77" s="3"/>
+      <c r="AK77" s="3"/>
+      <c r="AL77" s="3"/>
+      <c r="AM77" s="3"/>
+      <c r="AN77" s="3"/>
+      <c r="AO77" s="3"/>
+      <c r="AP77" s="3"/>
+    </row>
+    <row r="78" spans="1:42">
+      <c r="A78" s="2"/>
+      <c r="B78" s="3" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="65" spans="2:4">
-      <c r="B65" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="C65" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="D65" s="1" t="s">
+      <c r="C78" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="D78" s="4" t="s">
         <v>125</v>
       </c>
-    </row>
-    <row r="66" spans="2:4">
-      <c r="B66" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="C66" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="D66" s="1" t="s">
+      <c r="E78" s="4"/>
+      <c r="F78" s="4"/>
+      <c r="G78" s="4"/>
+      <c r="H78" s="4"/>
+      <c r="I78" s="4"/>
+      <c r="J78" s="3"/>
+      <c r="K78" s="4"/>
+      <c r="L78" s="4"/>
+      <c r="M78" s="4"/>
+      <c r="N78" s="4"/>
+      <c r="O78"/>
+      <c r="P78"/>
+      <c r="Q78"/>
+      <c r="R78"/>
+      <c r="T78" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="U78" s="4"/>
+      <c r="W78" s="4"/>
+      <c r="X78" s="4"/>
+      <c r="Y78" s="4"/>
+      <c r="Z78" s="3"/>
+      <c r="AA78" s="3"/>
+      <c r="AB78" s="3"/>
+      <c r="AC78" s="3"/>
+      <c r="AD78" s="3"/>
+      <c r="AE78" s="3"/>
+      <c r="AF78" s="3"/>
+      <c r="AG78" s="3"/>
+      <c r="AH78" s="3"/>
+      <c r="AI78" s="3"/>
+      <c r="AJ78" s="3"/>
+      <c r="AK78" s="3"/>
+      <c r="AL78" s="3"/>
+      <c r="AM78" s="3"/>
+      <c r="AN78" s="3"/>
+      <c r="AO78" s="3"/>
+      <c r="AP78" s="3"/>
+    </row>
+    <row r="79" spans="1:42">
+      <c r="A79" s="2"/>
+      <c r="B79" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="C79" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="D79" s="4" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="67" spans="2:4">
-      <c r="B67" s="1" t="s">
+      <c r="E79" s="4"/>
+      <c r="F79" s="4"/>
+      <c r="G79" s="4"/>
+      <c r="H79" s="4"/>
+      <c r="I79" s="4"/>
+      <c r="J79" s="3"/>
+      <c r="K79" s="4"/>
+      <c r="L79" s="4"/>
+      <c r="M79" s="4"/>
+      <c r="N79" s="4"/>
+      <c r="O79"/>
+      <c r="P79"/>
+      <c r="Q79"/>
+      <c r="R79"/>
+      <c r="T79" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="U79" s="4"/>
+      <c r="W79" s="4"/>
+      <c r="X79" s="4"/>
+      <c r="Y79" s="4"/>
+      <c r="Z79" s="3"/>
+      <c r="AA79" s="3"/>
+      <c r="AB79" s="3"/>
+      <c r="AC79" s="3"/>
+      <c r="AD79" s="3"/>
+      <c r="AE79" s="3"/>
+      <c r="AF79" s="3"/>
+      <c r="AG79" s="3"/>
+      <c r="AH79" s="3"/>
+      <c r="AI79" s="3"/>
+      <c r="AJ79" s="3"/>
+      <c r="AK79" s="3"/>
+      <c r="AL79" s="3"/>
+      <c r="AM79" s="3"/>
+      <c r="AN79" s="3"/>
+      <c r="AO79" s="3"/>
+      <c r="AP79" s="3"/>
+    </row>
+    <row r="80" spans="1:41">
+      <c r="A80" s="2"/>
+      <c r="B80" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="C67" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="D67" s="1" t="s">
+      <c r="C80" s="4" t="s">
         <v>128</v>
       </c>
-    </row>
-    <row r="68" spans="2:4">
-      <c r="B68" s="1" t="s">
+      <c r="D80" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="E80" s="4"/>
+      <c r="F80" s="4"/>
+      <c r="G80" s="4"/>
+      <c r="H80" s="4"/>
+      <c r="I80" s="4"/>
+      <c r="J80" s="3"/>
+      <c r="K80" s="4"/>
+      <c r="L80" s="4"/>
+      <c r="M80" s="4"/>
+      <c r="N80" s="4"/>
+      <c r="O80"/>
+      <c r="P80"/>
+      <c r="Q80"/>
+      <c r="R80"/>
+      <c r="T80" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="U80" s="4"/>
+      <c r="W80" s="4"/>
+      <c r="X80" s="4"/>
+      <c r="Y80" s="4"/>
+      <c r="Z80" s="3"/>
+      <c r="AA80" s="3"/>
+      <c r="AB80" s="3"/>
+      <c r="AC80" s="3"/>
+      <c r="AD80" s="3"/>
+      <c r="AE80" s="3"/>
+      <c r="AF80" s="3"/>
+      <c r="AG80" s="3"/>
+      <c r="AH80" s="3"/>
+      <c r="AI80" s="3"/>
+      <c r="AJ80" s="3"/>
+      <c r="AK80" s="3"/>
+      <c r="AL80" s="3"/>
+      <c r="AM80" s="3"/>
+      <c r="AN80" s="3"/>
+      <c r="AO80" s="3"/>
+    </row>
+    <row r="81" spans="1:41">
+      <c r="A81" s="2"/>
+      <c r="B81" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="C68" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="D68" s="1" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="69" spans="2:4">
-      <c r="B69" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="C69" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="D69" s="1" t="s">
+      <c r="C81" s="4" t="s">
         <v>130</v>
       </c>
-    </row>
-    <row r="70" spans="2:4">
-      <c r="B70" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="C70" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="D70" s="1" t="s">
+      <c r="D81" s="4" t="s">
         <v>131</v>
       </c>
-    </row>
-    <row r="71" spans="2:4">
-      <c r="B71" s="1" t="s">
+      <c r="E81" s="4"/>
+      <c r="F81" s="4"/>
+      <c r="G81" s="4"/>
+      <c r="H81" s="4"/>
+      <c r="I81" s="4"/>
+      <c r="J81" s="3"/>
+      <c r="K81" s="4"/>
+      <c r="L81" s="4"/>
+      <c r="M81" s="4"/>
+      <c r="N81" s="4"/>
+      <c r="O81"/>
+      <c r="P81"/>
+      <c r="Q81"/>
+      <c r="R81"/>
+      <c r="T81" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="U81" s="4"/>
+      <c r="W81" s="4"/>
+      <c r="X81" s="4"/>
+      <c r="Y81" s="4"/>
+      <c r="Z81" s="3"/>
+      <c r="AA81" s="3"/>
+      <c r="AB81" s="3"/>
+      <c r="AC81" s="3"/>
+      <c r="AD81" s="3"/>
+      <c r="AE81" s="3"/>
+      <c r="AF81" s="3"/>
+      <c r="AG81" s="3"/>
+      <c r="AH81" s="3"/>
+      <c r="AI81" s="3"/>
+      <c r="AJ81" s="3"/>
+      <c r="AK81" s="3"/>
+      <c r="AL81" s="3"/>
+      <c r="AM81" s="3"/>
+      <c r="AN81" s="3"/>
+      <c r="AO81" s="3"/>
+    </row>
+    <row r="82" spans="1:41">
+      <c r="A82" s="2"/>
+      <c r="B82" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="C71" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="D71" s="1" t="s">
+      <c r="C82" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="D82" s="4" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="72" spans="2:4">
-      <c r="B72" s="1" t="s">
+      <c r="E82" s="4"/>
+      <c r="F82" s="4"/>
+      <c r="G82" s="4"/>
+      <c r="H82" s="4"/>
+      <c r="I82" s="4"/>
+      <c r="J82" s="3"/>
+      <c r="K82" s="4"/>
+      <c r="L82" s="4"/>
+      <c r="M82" s="4"/>
+      <c r="N82" s="4"/>
+      <c r="O82"/>
+      <c r="P82"/>
+      <c r="Q82"/>
+      <c r="R82"/>
+      <c r="T82" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="U82" s="4"/>
+      <c r="W82" s="4"/>
+      <c r="X82" s="4"/>
+      <c r="Y82" s="4"/>
+      <c r="Z82" s="3"/>
+      <c r="AA82" s="3"/>
+      <c r="AB82" s="3"/>
+      <c r="AC82" s="3"/>
+      <c r="AD82" s="3"/>
+      <c r="AE82" s="3"/>
+      <c r="AF82" s="3"/>
+      <c r="AG82" s="3"/>
+      <c r="AH82" s="3"/>
+      <c r="AI82" s="3"/>
+      <c r="AJ82" s="3"/>
+      <c r="AK82" s="3"/>
+      <c r="AL82" s="3"/>
+      <c r="AM82" s="3"/>
+      <c r="AN82" s="3"/>
+      <c r="AO82" s="3"/>
+    </row>
+    <row r="83" spans="1:41">
+      <c r="A83" s="2"/>
+      <c r="B83" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="C72" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="D72" s="1" t="s">
+      <c r="C83" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="D83" s="4" t="s">
         <v>134</v>
       </c>
-    </row>
-    <row r="73" spans="2:4">
-      <c r="B73" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="C73" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="D73" s="1" t="s">
+      <c r="E83" s="4"/>
+      <c r="F83" s="4"/>
+      <c r="G83" s="4"/>
+      <c r="H83" s="4"/>
+      <c r="I83" s="4"/>
+      <c r="J83" s="3"/>
+      <c r="K83" s="4"/>
+      <c r="L83" s="4"/>
+      <c r="M83" s="4"/>
+      <c r="N83" s="4"/>
+      <c r="O83"/>
+      <c r="P83"/>
+      <c r="Q83"/>
+      <c r="R83"/>
+      <c r="T83" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="U83" s="4"/>
+      <c r="W83" s="4"/>
+      <c r="X83" s="4"/>
+      <c r="Y83" s="4"/>
+      <c r="Z83" s="3"/>
+      <c r="AA83" s="3"/>
+      <c r="AB83" s="3"/>
+      <c r="AC83" s="3"/>
+      <c r="AD83" s="3"/>
+      <c r="AE83" s="3"/>
+      <c r="AF83" s="3"/>
+      <c r="AG83" s="3"/>
+      <c r="AH83" s="3"/>
+      <c r="AI83" s="3"/>
+      <c r="AJ83" s="3"/>
+      <c r="AK83" s="3"/>
+      <c r="AL83" s="3"/>
+      <c r="AM83" s="3"/>
+      <c r="AN83" s="3"/>
+      <c r="AO83" s="3"/>
+    </row>
+    <row r="84" spans="1:41">
+      <c r="A84" s="2"/>
+      <c r="B84" s="3" t="s">
         <v>135</v>
       </c>
-    </row>
-    <row r="74" spans="2:4">
-      <c r="B74" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="C74" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="D74" s="1" t="s">
+      <c r="C84" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="D84" s="4" t="s">
         <v>136</v>
       </c>
-    </row>
-    <row r="75" spans="2:4">
-      <c r="B75" s="1" t="s">
+      <c r="E84" s="4"/>
+      <c r="F84" s="4"/>
+      <c r="G84" s="4"/>
+      <c r="H84" s="4"/>
+      <c r="I84" s="4"/>
+      <c r="J84" s="3"/>
+      <c r="K84" s="4"/>
+      <c r="L84" s="4"/>
+      <c r="M84" s="4"/>
+      <c r="N84" s="4"/>
+      <c r="O84"/>
+      <c r="P84"/>
+      <c r="Q84"/>
+      <c r="R84"/>
+      <c r="T84" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="U84" s="4"/>
+      <c r="W84" s="4"/>
+      <c r="X84" s="4"/>
+      <c r="Y84" s="4"/>
+      <c r="Z84" s="3"/>
+      <c r="AA84" s="3"/>
+      <c r="AB84" s="3"/>
+      <c r="AC84" s="3"/>
+      <c r="AD84" s="3"/>
+      <c r="AE84" s="3"/>
+      <c r="AF84" s="3"/>
+      <c r="AG84" s="3"/>
+      <c r="AH84" s="3"/>
+      <c r="AI84" s="3"/>
+      <c r="AJ84" s="3"/>
+      <c r="AK84" s="3"/>
+      <c r="AL84" s="3"/>
+      <c r="AM84" s="3"/>
+      <c r="AN84" s="3"/>
+      <c r="AO84" s="3"/>
+    </row>
+    <row r="85" spans="1:41">
+      <c r="A85" s="2"/>
+      <c r="B85" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C85" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="D85" s="4" t="s">
         <v>137</v>
       </c>
-      <c r="C75" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="D75" s="1" t="s">
+      <c r="E85" s="4"/>
+      <c r="F85" s="4"/>
+      <c r="G85" s="4"/>
+      <c r="H85" s="4"/>
+      <c r="I85" s="4"/>
+      <c r="J85" s="3"/>
+      <c r="K85" s="4"/>
+      <c r="L85" s="4"/>
+      <c r="M85" s="4"/>
+      <c r="N85" s="4"/>
+      <c r="O85"/>
+      <c r="P85"/>
+      <c r="Q85"/>
+      <c r="R85"/>
+      <c r="T85" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="U85" s="4"/>
+      <c r="W85" s="4"/>
+      <c r="X85" s="4"/>
+      <c r="Y85" s="4"/>
+      <c r="Z85" s="3"/>
+      <c r="AA85" s="3"/>
+      <c r="AB85" s="3"/>
+      <c r="AC85" s="3"/>
+      <c r="AD85" s="3"/>
+      <c r="AE85" s="3"/>
+      <c r="AF85" s="3"/>
+      <c r="AG85" s="3"/>
+      <c r="AH85" s="3"/>
+      <c r="AI85" s="3"/>
+      <c r="AJ85" s="3"/>
+      <c r="AK85" s="3"/>
+      <c r="AL85" s="3"/>
+      <c r="AM85" s="3"/>
+      <c r="AN85" s="3"/>
+      <c r="AO85" s="3"/>
+    </row>
+    <row r="86" spans="1:41">
+      <c r="A86" s="2"/>
+      <c r="B86" s="3" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="76" spans="2:4">
-      <c r="B76" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="C76" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="D76" s="1" t="s">
+      <c r="C86" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="D86" s="4" t="s">
         <v>139</v>
       </c>
-    </row>
-    <row r="77" spans="2:4">
-      <c r="B77" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="C77" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="D77" s="1" t="s">
+      <c r="E86" s="4"/>
+      <c r="F86" s="4"/>
+      <c r="G86" s="4"/>
+      <c r="H86" s="4"/>
+      <c r="I86" s="4"/>
+      <c r="J86" s="3"/>
+      <c r="K86" s="4"/>
+      <c r="L86" s="4"/>
+      <c r="M86" s="4"/>
+      <c r="N86" s="4"/>
+      <c r="O86"/>
+      <c r="P86"/>
+      <c r="Q86"/>
+      <c r="R86"/>
+      <c r="T86" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="U86" s="4"/>
+      <c r="W86" s="4"/>
+      <c r="X86" s="4"/>
+      <c r="Y86" s="4"/>
+      <c r="Z86" s="3"/>
+      <c r="AA86" s="3"/>
+      <c r="AB86" s="3"/>
+      <c r="AC86" s="3"/>
+      <c r="AD86" s="3"/>
+      <c r="AE86" s="3"/>
+      <c r="AF86" s="3"/>
+      <c r="AG86" s="3"/>
+      <c r="AH86" s="3"/>
+      <c r="AI86" s="3"/>
+      <c r="AJ86" s="3"/>
+      <c r="AK86" s="3"/>
+      <c r="AL86" s="3"/>
+      <c r="AM86" s="3"/>
+      <c r="AN86" s="3"/>
+      <c r="AO86" s="3"/>
+    </row>
+    <row r="87" spans="1:41">
+      <c r="A87" s="2"/>
+      <c r="B87" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="C87" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="D87" s="4" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="78" spans="2:4">
-      <c r="B78" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="C78" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="D78" s="1" t="s">
+      <c r="E87" s="4"/>
+      <c r="F87" s="4"/>
+      <c r="G87" s="4"/>
+      <c r="H87" s="4"/>
+      <c r="I87" s="4"/>
+      <c r="J87" s="3"/>
+      <c r="K87" s="4"/>
+      <c r="L87" s="4"/>
+      <c r="M87" s="4"/>
+      <c r="N87" s="4"/>
+      <c r="O87"/>
+      <c r="P87"/>
+      <c r="Q87"/>
+      <c r="R87"/>
+      <c r="T87" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="U87" s="4"/>
+      <c r="W87" s="4"/>
+      <c r="X87" s="4"/>
+      <c r="Y87" s="4"/>
+      <c r="Z87" s="3"/>
+      <c r="AA87" s="3"/>
+      <c r="AB87" s="3"/>
+      <c r="AC87" s="3"/>
+      <c r="AD87" s="3"/>
+      <c r="AE87" s="3"/>
+      <c r="AF87" s="3"/>
+      <c r="AG87" s="3"/>
+      <c r="AH87" s="3"/>
+      <c r="AI87" s="3"/>
+      <c r="AJ87" s="3"/>
+      <c r="AK87" s="3"/>
+      <c r="AL87" s="3"/>
+      <c r="AM87" s="3"/>
+      <c r="AN87" s="3"/>
+      <c r="AO87" s="3"/>
+    </row>
+    <row r="88" spans="1:41">
+      <c r="A88" s="2"/>
+      <c r="B88" s="3" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="79" spans="2:4">
-      <c r="B79" s="1" t="s">
+      <c r="C88" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="D88" s="4" t="s">
         <v>142</v>
       </c>
-      <c r="C79" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="D79" s="1" t="s">
+      <c r="E88" s="4"/>
+      <c r="F88" s="4"/>
+      <c r="G88" s="4"/>
+      <c r="H88" s="4"/>
+      <c r="I88" s="4"/>
+      <c r="J88" s="3"/>
+      <c r="K88" s="4"/>
+      <c r="L88" s="4"/>
+      <c r="M88" s="4"/>
+      <c r="N88" s="4"/>
+      <c r="O88"/>
+      <c r="P88"/>
+      <c r="Q88"/>
+      <c r="R88"/>
+      <c r="T88" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="U88" s="4"/>
+      <c r="W88" s="4"/>
+      <c r="X88" s="4"/>
+      <c r="Y88" s="4"/>
+      <c r="Z88" s="3"/>
+      <c r="AA88" s="3"/>
+      <c r="AB88" s="3"/>
+      <c r="AC88" s="3"/>
+      <c r="AD88" s="3"/>
+      <c r="AE88" s="3"/>
+      <c r="AF88" s="3"/>
+      <c r="AG88" s="3"/>
+      <c r="AH88" s="3"/>
+      <c r="AI88" s="3"/>
+      <c r="AJ88" s="3"/>
+      <c r="AK88" s="3"/>
+      <c r="AL88" s="3"/>
+      <c r="AM88" s="3"/>
+      <c r="AN88" s="3"/>
+      <c r="AO88" s="3"/>
+    </row>
+    <row r="89" spans="1:41">
+      <c r="A89" s="2"/>
+      <c r="B89" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="C89" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="D89" s="4" t="s">
         <v>143</v>
       </c>
-    </row>
-    <row r="80" spans="2:4">
-      <c r="B80" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="C80" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="D80" s="1" t="s">
+      <c r="E89" s="4"/>
+      <c r="F89" s="4"/>
+      <c r="G89" s="4"/>
+      <c r="H89" s="4"/>
+      <c r="I89" s="4"/>
+      <c r="J89" s="3"/>
+      <c r="K89" s="4"/>
+      <c r="L89" s="4"/>
+      <c r="M89" s="4"/>
+      <c r="N89" s="4"/>
+      <c r="O89"/>
+      <c r="P89"/>
+      <c r="Q89"/>
+      <c r="R89"/>
+      <c r="T89" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="U89" s="4"/>
+      <c r="W89" s="4"/>
+      <c r="X89" s="4"/>
+      <c r="Y89" s="4"/>
+      <c r="Z89" s="3"/>
+      <c r="AA89" s="3"/>
+      <c r="AB89" s="3"/>
+      <c r="AC89" s="3"/>
+      <c r="AD89" s="3"/>
+      <c r="AE89" s="3"/>
+      <c r="AF89" s="3"/>
+      <c r="AG89" s="3"/>
+      <c r="AH89" s="3"/>
+      <c r="AI89" s="3"/>
+      <c r="AJ89" s="3"/>
+      <c r="AK89" s="3"/>
+      <c r="AL89" s="3"/>
+      <c r="AM89" s="3"/>
+      <c r="AN89" s="3"/>
+      <c r="AO89" s="3"/>
+    </row>
+    <row r="90" spans="1:41">
+      <c r="A90" s="2"/>
+      <c r="B90" s="3" t="s">
         <v>144</v>
       </c>
-    </row>
-    <row r="81" spans="2:4">
-      <c r="B81" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="C81" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="D81" s="1" t="s">
+      <c r="C90" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="D90" s="4" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="82" spans="2:4">
-      <c r="B82" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="C82" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="D82" s="1" t="s">
+      <c r="E90" s="4"/>
+      <c r="F90" s="4"/>
+      <c r="G90" s="4"/>
+      <c r="H90" s="4"/>
+      <c r="I90" s="4"/>
+      <c r="J90" s="3"/>
+      <c r="K90" s="4"/>
+      <c r="L90" s="4"/>
+      <c r="M90" s="4"/>
+      <c r="N90" s="4"/>
+      <c r="O90"/>
+      <c r="P90"/>
+      <c r="Q90"/>
+      <c r="R90"/>
+      <c r="T90" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="U90" s="4"/>
+      <c r="W90" s="4"/>
+      <c r="X90" s="4"/>
+      <c r="Y90" s="4"/>
+      <c r="Z90" s="3"/>
+      <c r="AA90" s="3"/>
+      <c r="AB90" s="3"/>
+      <c r="AC90" s="3"/>
+      <c r="AD90" s="3"/>
+      <c r="AE90" s="3"/>
+      <c r="AF90" s="3"/>
+      <c r="AG90" s="3"/>
+      <c r="AH90" s="3"/>
+      <c r="AI90" s="3"/>
+      <c r="AJ90" s="3"/>
+      <c r="AK90" s="3"/>
+      <c r="AL90" s="3"/>
+      <c r="AM90" s="3"/>
+      <c r="AN90" s="3"/>
+      <c r="AO90" s="3"/>
+    </row>
+    <row r="91" spans="1:41">
+      <c r="A91" s="2"/>
+      <c r="B91" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="C91" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="D91" s="4" t="s">
         <v>146</v>
       </c>
-    </row>
-    <row r="83" spans="2:4">
-      <c r="B83" s="1" t="s">
+      <c r="E91" s="4"/>
+      <c r="F91" s="4"/>
+      <c r="G91" s="4"/>
+      <c r="H91" s="4"/>
+      <c r="I91" s="4"/>
+      <c r="J91" s="3"/>
+      <c r="K91" s="4"/>
+      <c r="L91" s="4"/>
+      <c r="M91" s="4"/>
+      <c r="N91" s="4"/>
+      <c r="O91"/>
+      <c r="P91"/>
+      <c r="Q91"/>
+      <c r="R91"/>
+      <c r="T91" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="U91" s="4"/>
+      <c r="W91" s="4"/>
+      <c r="X91" s="4"/>
+      <c r="Y91" s="4"/>
+      <c r="Z91" s="3"/>
+      <c r="AA91" s="3"/>
+      <c r="AB91" s="3"/>
+      <c r="AC91" s="3"/>
+      <c r="AD91" s="3"/>
+      <c r="AE91" s="3"/>
+      <c r="AF91" s="3"/>
+      <c r="AG91" s="3"/>
+      <c r="AH91" s="3"/>
+      <c r="AI91" s="3"/>
+      <c r="AJ91" s="3"/>
+      <c r="AK91" s="3"/>
+      <c r="AL91" s="3"/>
+      <c r="AM91" s="3"/>
+      <c r="AN91" s="3"/>
+      <c r="AO91" s="3"/>
+    </row>
+    <row r="92" spans="1:41">
+      <c r="A92" s="2"/>
+      <c r="B92" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="C83" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="D83" s="1" t="s">
+      <c r="C92" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="D92" s="4" t="s">
         <v>148</v>
       </c>
-    </row>
-    <row r="84" spans="2:4">
-      <c r="B84" s="1" t="s">
+      <c r="E92" s="4"/>
+      <c r="F92" s="4"/>
+      <c r="G92" s="4"/>
+      <c r="H92" s="4"/>
+      <c r="I92" s="4"/>
+      <c r="J92" s="3"/>
+      <c r="K92" s="4"/>
+      <c r="L92" s="4"/>
+      <c r="M92" s="4"/>
+      <c r="N92" s="4"/>
+      <c r="O92"/>
+      <c r="P92"/>
+      <c r="Q92"/>
+      <c r="R92"/>
+      <c r="T92" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="U92" s="4"/>
+      <c r="W92" s="4"/>
+      <c r="X92" s="4"/>
+      <c r="Y92" s="4"/>
+      <c r="Z92" s="3"/>
+      <c r="AA92" s="3"/>
+      <c r="AB92" s="3"/>
+      <c r="AC92" s="3"/>
+      <c r="AD92" s="3"/>
+      <c r="AE92" s="3"/>
+      <c r="AF92" s="3"/>
+      <c r="AG92" s="3"/>
+      <c r="AH92" s="3"/>
+      <c r="AI92" s="3"/>
+      <c r="AJ92" s="3"/>
+      <c r="AK92" s="3"/>
+      <c r="AL92" s="3"/>
+      <c r="AM92" s="3"/>
+      <c r="AN92" s="3"/>
+      <c r="AO92" s="3"/>
+    </row>
+    <row r="93" spans="1:41">
+      <c r="A93" s="2"/>
+      <c r="B93" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="C84" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="D84" s="1" t="s">
+      <c r="C93" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="D93" s="4" t="s">
         <v>149</v>
       </c>
-    </row>
-    <row r="85" spans="2:4">
-      <c r="B85" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="C85" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="D85" s="1" t="s">
+      <c r="E93" s="4"/>
+      <c r="F93" s="4"/>
+      <c r="G93" s="4"/>
+      <c r="H93" s="4"/>
+      <c r="I93" s="4"/>
+      <c r="J93" s="3"/>
+      <c r="K93" s="4"/>
+      <c r="L93" s="4"/>
+      <c r="M93" s="4"/>
+      <c r="N93" s="4"/>
+      <c r="O93"/>
+      <c r="P93"/>
+      <c r="Q93"/>
+      <c r="R93"/>
+      <c r="T93" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="U93" s="4"/>
+      <c r="W93" s="4"/>
+      <c r="X93" s="4"/>
+      <c r="Y93" s="4"/>
+      <c r="Z93" s="3"/>
+      <c r="AA93" s="3"/>
+      <c r="AB93" s="3"/>
+      <c r="AC93" s="3"/>
+      <c r="AD93" s="3"/>
+      <c r="AE93" s="3"/>
+      <c r="AF93" s="3"/>
+      <c r="AG93" s="3"/>
+      <c r="AH93" s="3"/>
+      <c r="AI93" s="3"/>
+      <c r="AJ93" s="3"/>
+      <c r="AK93" s="3"/>
+      <c r="AL93" s="3"/>
+      <c r="AM93" s="3"/>
+      <c r="AN93" s="3"/>
+      <c r="AO93" s="3"/>
+    </row>
+    <row r="94" spans="1:41">
+      <c r="A94" s="2"/>
+      <c r="B94" s="3" t="s">
         <v>150</v>
       </c>
-    </row>
-    <row r="86" spans="2:4">
-      <c r="B86" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="C86" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="D86" s="1" t="s">
+      <c r="C94" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="D94" s="4" t="s">
         <v>151</v>
       </c>
-    </row>
-    <row r="87" spans="2:4">
-      <c r="B87" s="1" t="s">
+      <c r="E94" s="4"/>
+      <c r="F94" s="4"/>
+      <c r="G94" s="4"/>
+      <c r="H94" s="4"/>
+      <c r="I94" s="4"/>
+      <c r="J94" s="3"/>
+      <c r="K94" s="4"/>
+      <c r="L94" s="4"/>
+      <c r="M94" s="4"/>
+      <c r="N94" s="4"/>
+      <c r="O94"/>
+      <c r="P94"/>
+      <c r="Q94"/>
+      <c r="R94"/>
+      <c r="T94" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="U94" s="4"/>
+      <c r="W94" s="4"/>
+      <c r="X94" s="4"/>
+      <c r="Y94" s="4"/>
+      <c r="Z94" s="3"/>
+      <c r="AA94" s="3"/>
+      <c r="AB94" s="3"/>
+      <c r="AC94" s="3"/>
+      <c r="AD94" s="3"/>
+      <c r="AE94" s="3"/>
+      <c r="AF94" s="3"/>
+      <c r="AG94" s="3"/>
+      <c r="AH94" s="3"/>
+      <c r="AI94" s="3"/>
+      <c r="AJ94" s="3"/>
+      <c r="AK94" s="3"/>
+      <c r="AL94" s="3"/>
+      <c r="AM94" s="3"/>
+      <c r="AN94" s="3"/>
+      <c r="AO94" s="3"/>
+    </row>
+    <row r="95" spans="1:41">
+      <c r="A95" s="2"/>
+      <c r="B95" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="C95" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="D95" s="4" t="s">
         <v>152</v>
       </c>
-      <c r="C87" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="D87" s="1" t="s">
+      <c r="E95" s="4"/>
+      <c r="F95" s="4"/>
+      <c r="G95" s="4"/>
+      <c r="H95" s="4"/>
+      <c r="I95" s="4"/>
+      <c r="J95" s="3"/>
+      <c r="K95" s="4"/>
+      <c r="L95" s="4"/>
+      <c r="M95" s="4"/>
+      <c r="N95" s="4"/>
+      <c r="O95"/>
+      <c r="P95"/>
+      <c r="Q95"/>
+      <c r="R95"/>
+      <c r="T95" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="U95" s="4"/>
+      <c r="W95" s="4"/>
+      <c r="X95" s="4"/>
+      <c r="Y95" s="4"/>
+      <c r="Z95" s="3"/>
+      <c r="AA95" s="3"/>
+      <c r="AB95" s="3"/>
+      <c r="AC95" s="3"/>
+      <c r="AD95" s="3"/>
+      <c r="AE95" s="3"/>
+      <c r="AF95" s="3"/>
+      <c r="AG95" s="3"/>
+      <c r="AH95" s="3"/>
+      <c r="AI95" s="3"/>
+      <c r="AJ95" s="3"/>
+      <c r="AK95" s="3"/>
+      <c r="AL95" s="3"/>
+      <c r="AM95" s="3"/>
+      <c r="AN95" s="3"/>
+      <c r="AO95" s="3"/>
+    </row>
+    <row r="96" spans="1:41">
+      <c r="A96" s="2"/>
+      <c r="B96" s="3" t="s">
         <v>153</v>
       </c>
-    </row>
-    <row r="88" spans="2:4">
-      <c r="B88" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="C88" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="D88" s="1" t="s">
+      <c r="C96" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="D96" s="4" t="s">
         <v>154</v>
       </c>
-    </row>
-    <row r="89" spans="2:4">
-      <c r="B89" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="C89" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="D89" s="1" t="s">
+      <c r="E96" s="4"/>
+      <c r="F96" s="4"/>
+      <c r="G96" s="4"/>
+      <c r="H96" s="4"/>
+      <c r="I96" s="4"/>
+      <c r="J96" s="3"/>
+      <c r="K96" s="4"/>
+      <c r="L96" s="4"/>
+      <c r="M96" s="4"/>
+      <c r="N96" s="4"/>
+      <c r="O96"/>
+      <c r="P96"/>
+      <c r="Q96"/>
+      <c r="R96"/>
+      <c r="T96" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="U96" s="4"/>
+      <c r="W96" s="4"/>
+      <c r="X96" s="4"/>
+      <c r="Y96" s="4"/>
+      <c r="Z96" s="3"/>
+      <c r="AA96" s="3"/>
+      <c r="AB96" s="3"/>
+      <c r="AC96" s="3"/>
+      <c r="AD96" s="3"/>
+      <c r="AE96" s="3"/>
+      <c r="AF96" s="3"/>
+      <c r="AG96" s="3"/>
+      <c r="AH96" s="3"/>
+      <c r="AI96" s="3"/>
+      <c r="AJ96" s="3"/>
+      <c r="AK96" s="3"/>
+      <c r="AL96" s="3"/>
+      <c r="AM96" s="3"/>
+      <c r="AN96" s="3"/>
+      <c r="AO96" s="3"/>
+    </row>
+    <row r="97" spans="1:41">
+      <c r="A97" s="2"/>
+      <c r="B97" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="C97" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="D97" s="4" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="90" spans="2:4">
-      <c r="B90" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="C90" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="D90" s="1" t="s">
+      <c r="E97" s="4"/>
+      <c r="F97" s="4"/>
+      <c r="G97" s="4"/>
+      <c r="H97" s="4"/>
+      <c r="I97" s="4"/>
+      <c r="J97" s="3"/>
+      <c r="K97" s="4"/>
+      <c r="L97" s="4"/>
+      <c r="M97" s="4"/>
+      <c r="N97" s="4"/>
+      <c r="O97"/>
+      <c r="P97"/>
+      <c r="Q97"/>
+      <c r="R97"/>
+      <c r="T97" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="U97" s="4"/>
+      <c r="W97" s="4"/>
+      <c r="X97" s="4"/>
+      <c r="Y97" s="4"/>
+      <c r="Z97" s="3"/>
+      <c r="AA97" s="3"/>
+      <c r="AB97" s="3"/>
+      <c r="AC97" s="3"/>
+      <c r="AD97" s="3"/>
+      <c r="AE97" s="3"/>
+      <c r="AF97" s="3"/>
+      <c r="AG97" s="3"/>
+      <c r="AH97" s="3"/>
+      <c r="AI97" s="3"/>
+      <c r="AJ97" s="3"/>
+      <c r="AK97" s="3"/>
+      <c r="AL97" s="3"/>
+      <c r="AM97" s="3"/>
+      <c r="AN97" s="3"/>
+      <c r="AO97" s="3"/>
+    </row>
+    <row r="98" spans="1:41">
+      <c r="A98" s="2"/>
+      <c r="B98" s="3" t="s">
         <v>156</v>
       </c>
+      <c r="C98" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="D98" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="E98" s="4"/>
+      <c r="F98" s="4"/>
+      <c r="G98" s="4"/>
+      <c r="H98" s="4"/>
+      <c r="I98" s="4"/>
+      <c r="J98" s="3"/>
+      <c r="K98" s="4"/>
+      <c r="L98" s="4"/>
+      <c r="M98" s="4"/>
+      <c r="N98" s="4"/>
+      <c r="O98"/>
+      <c r="P98"/>
+      <c r="Q98"/>
+      <c r="R98"/>
+      <c r="T98" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="U98" s="4"/>
+      <c r="W98" s="4"/>
+      <c r="X98" s="4"/>
+      <c r="Y98" s="4"/>
+      <c r="Z98" s="3"/>
+      <c r="AA98" s="3"/>
+      <c r="AB98" s="3"/>
+      <c r="AC98" s="3"/>
+      <c r="AD98" s="3"/>
+      <c r="AE98" s="3"/>
+      <c r="AF98" s="3"/>
+      <c r="AG98" s="3"/>
+      <c r="AH98" s="3"/>
+      <c r="AI98" s="3"/>
+      <c r="AJ98" s="3"/>
+      <c r="AK98" s="3"/>
+      <c r="AL98" s="3"/>
+      <c r="AM98" s="3"/>
+      <c r="AN98" s="3"/>
+      <c r="AO98" s="3"/>
+    </row>
+    <row r="99" spans="1:41">
+      <c r="A99" s="2"/>
+      <c r="B99" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="C99" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="D99" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="E99" s="4"/>
+      <c r="F99" s="4"/>
+      <c r="G99" s="4"/>
+      <c r="H99" s="4"/>
+      <c r="I99" s="4"/>
+      <c r="J99" s="3"/>
+      <c r="K99" s="4"/>
+      <c r="L99" s="4"/>
+      <c r="M99" s="4"/>
+      <c r="N99" s="4"/>
+      <c r="O99"/>
+      <c r="P99"/>
+      <c r="Q99"/>
+      <c r="R99"/>
+      <c r="T99" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="U99" s="4"/>
+      <c r="W99" s="4"/>
+      <c r="X99" s="4"/>
+      <c r="Y99" s="4"/>
+      <c r="Z99" s="3"/>
+      <c r="AA99" s="3"/>
+      <c r="AB99" s="3"/>
+      <c r="AC99" s="3"/>
+      <c r="AD99" s="3"/>
+      <c r="AE99" s="3"/>
+      <c r="AF99" s="3"/>
+      <c r="AG99" s="3"/>
+      <c r="AH99" s="3"/>
+      <c r="AI99" s="3"/>
+      <c r="AJ99" s="3"/>
+      <c r="AK99" s="3"/>
+      <c r="AL99" s="3"/>
+      <c r="AM99" s="3"/>
+      <c r="AN99" s="3"/>
+      <c r="AO99" s="3"/>
+    </row>
+    <row r="100" spans="1:41">
+      <c r="A100" s="2"/>
+      <c r="B100" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="C100" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="D100" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="E100" s="4"/>
+      <c r="F100" s="4"/>
+      <c r="G100" s="4"/>
+      <c r="H100" s="4"/>
+      <c r="I100" s="4"/>
+      <c r="J100" s="3"/>
+      <c r="K100" s="4"/>
+      <c r="L100" s="4"/>
+      <c r="M100" s="4"/>
+      <c r="N100" s="4"/>
+      <c r="O100"/>
+      <c r="P100"/>
+      <c r="Q100"/>
+      <c r="R100"/>
+      <c r="T100" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="U100" s="4"/>
+      <c r="W100" s="4"/>
+      <c r="X100" s="4"/>
+      <c r="Y100" s="4"/>
+      <c r="Z100" s="3"/>
+      <c r="AA100" s="3"/>
+      <c r="AB100" s="3"/>
+      <c r="AC100" s="3"/>
+      <c r="AD100" s="3"/>
+      <c r="AE100" s="3"/>
+      <c r="AF100" s="3"/>
+      <c r="AG100" s="3"/>
+      <c r="AH100" s="3"/>
+      <c r="AI100" s="3"/>
+      <c r="AJ100" s="3"/>
+      <c r="AK100" s="3"/>
+      <c r="AL100" s="3"/>
+      <c r="AM100" s="3"/>
+      <c r="AN100" s="3"/>
+      <c r="AO100" s="3"/>
+    </row>
+    <row r="101" spans="1:41">
+      <c r="A101" s="2"/>
+      <c r="B101" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="C101" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="D101" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="E101" s="4"/>
+      <c r="F101" s="4"/>
+      <c r="G101" s="4"/>
+      <c r="H101" s="4"/>
+      <c r="I101" s="4"/>
+      <c r="J101" s="3"/>
+      <c r="K101" s="4"/>
+      <c r="L101" s="4"/>
+      <c r="M101" s="4"/>
+      <c r="N101" s="4"/>
+      <c r="O101"/>
+      <c r="P101"/>
+      <c r="Q101"/>
+      <c r="R101"/>
+      <c r="T101" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="U101" s="4"/>
+      <c r="W101" s="4"/>
+      <c r="X101" s="4"/>
+      <c r="Y101" s="4"/>
+      <c r="Z101" s="3"/>
+      <c r="AA101" s="3"/>
+      <c r="AB101" s="3"/>
+      <c r="AC101" s="3"/>
+      <c r="AD101" s="3"/>
+      <c r="AE101" s="3"/>
+      <c r="AF101" s="3"/>
+      <c r="AG101" s="3"/>
+      <c r="AH101" s="3"/>
+      <c r="AI101" s="3"/>
+      <c r="AJ101" s="3"/>
+      <c r="AK101" s="3"/>
+      <c r="AL101" s="3"/>
+      <c r="AM101" s="3"/>
+      <c r="AN101" s="3"/>
+      <c r="AO101" s="3"/>
+    </row>
+    <row r="102" spans="1:41">
+      <c r="A102" s="2"/>
+      <c r="B102" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="C102" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="D102" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="E102" s="4"/>
+      <c r="F102" s="4"/>
+      <c r="G102" s="4"/>
+      <c r="H102" s="4"/>
+      <c r="I102" s="4"/>
+      <c r="J102" s="3"/>
+      <c r="K102" s="4"/>
+      <c r="L102" s="4"/>
+      <c r="M102" s="4"/>
+      <c r="N102" s="4"/>
+      <c r="O102"/>
+      <c r="P102"/>
+      <c r="Q102"/>
+      <c r="R102"/>
+      <c r="T102" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="U102" s="4"/>
+      <c r="W102" s="4"/>
+      <c r="X102" s="4"/>
+      <c r="Y102" s="4"/>
+      <c r="Z102" s="3"/>
+      <c r="AA102" s="3"/>
+      <c r="AB102" s="3"/>
+      <c r="AC102" s="3"/>
+      <c r="AD102" s="3"/>
+      <c r="AE102" s="3"/>
+      <c r="AF102" s="3"/>
+      <c r="AG102" s="3"/>
+      <c r="AH102" s="3"/>
+      <c r="AI102" s="3"/>
+      <c r="AJ102" s="3"/>
+      <c r="AK102" s="3"/>
+      <c r="AL102" s="3"/>
+      <c r="AM102" s="3"/>
+      <c r="AN102" s="3"/>
+      <c r="AO102" s="3"/>
+    </row>
+    <row r="103" spans="1:41">
+      <c r="A103" s="2"/>
+      <c r="B103" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="C103" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="D103" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="E103" s="4"/>
+      <c r="F103" s="4"/>
+      <c r="G103" s="4"/>
+      <c r="H103" s="4"/>
+      <c r="I103" s="4"/>
+      <c r="J103" s="3"/>
+      <c r="K103" s="4"/>
+      <c r="L103" s="4"/>
+      <c r="M103" s="4"/>
+      <c r="N103" s="4"/>
+      <c r="O103"/>
+      <c r="P103"/>
+      <c r="Q103"/>
+      <c r="R103"/>
+      <c r="T103" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="U103" s="4"/>
+      <c r="W103" s="4"/>
+      <c r="X103" s="4"/>
+      <c r="Y103" s="4"/>
+      <c r="Z103" s="3"/>
+      <c r="AA103" s="3"/>
+      <c r="AB103" s="3"/>
+      <c r="AC103" s="3"/>
+      <c r="AD103" s="3"/>
+      <c r="AE103" s="3"/>
+      <c r="AF103" s="3"/>
+      <c r="AG103" s="3"/>
+      <c r="AH103" s="3"/>
+      <c r="AI103" s="3"/>
+      <c r="AJ103" s="3"/>
+      <c r="AK103" s="3"/>
+      <c r="AL103" s="3"/>
+      <c r="AM103" s="3"/>
+      <c r="AN103" s="3"/>
+      <c r="AO103" s="3"/>
+    </row>
+    <row r="104" spans="1:41">
+      <c r="A104" s="2"/>
+      <c r="B104" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="C104" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="D104" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="E104" s="4"/>
+      <c r="F104" s="4"/>
+      <c r="G104" s="4"/>
+      <c r="H104" s="4"/>
+      <c r="I104" s="4"/>
+      <c r="J104" s="3"/>
+      <c r="K104" s="4"/>
+      <c r="L104" s="4"/>
+      <c r="M104" s="4"/>
+      <c r="N104" s="4"/>
+      <c r="O104"/>
+      <c r="P104"/>
+      <c r="Q104"/>
+      <c r="R104"/>
+      <c r="T104" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="U104" s="4"/>
+      <c r="W104" s="4"/>
+      <c r="X104" s="4"/>
+      <c r="Y104" s="4"/>
+      <c r="Z104" s="3"/>
+      <c r="AA104" s="3"/>
+      <c r="AB104" s="3"/>
+      <c r="AC104" s="3"/>
+      <c r="AD104" s="3"/>
+      <c r="AE104" s="3"/>
+      <c r="AF104" s="3"/>
+      <c r="AG104" s="3"/>
+      <c r="AH104" s="3"/>
+      <c r="AI104" s="3"/>
+      <c r="AJ104" s="3"/>
+      <c r="AK104" s="3"/>
+      <c r="AL104" s="3"/>
+      <c r="AM104" s="3"/>
+      <c r="AN104" s="3"/>
+      <c r="AO104" s="3"/>
+    </row>
+    <row r="105" spans="1:41">
+      <c r="A105" s="2"/>
+      <c r="B105" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="C105" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="D105" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="E105" s="4"/>
+      <c r="F105" s="4"/>
+      <c r="G105" s="4"/>
+      <c r="H105" s="4"/>
+      <c r="I105" s="4"/>
+      <c r="J105" s="3"/>
+      <c r="K105" s="4"/>
+      <c r="L105" s="4"/>
+      <c r="M105" s="4"/>
+      <c r="N105" s="4"/>
+      <c r="O105"/>
+      <c r="P105"/>
+      <c r="Q105"/>
+      <c r="R105"/>
+      <c r="T105" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="U105" s="4"/>
+      <c r="W105" s="4"/>
+      <c r="X105" s="4"/>
+      <c r="Y105" s="4"/>
+      <c r="Z105" s="3"/>
+      <c r="AA105" s="3"/>
+      <c r="AB105" s="3"/>
+      <c r="AC105" s="3"/>
+      <c r="AD105" s="3"/>
+      <c r="AE105" s="3"/>
+      <c r="AF105" s="3"/>
+      <c r="AG105" s="3"/>
+      <c r="AH105" s="3"/>
+      <c r="AI105" s="3"/>
+      <c r="AJ105" s="3"/>
+      <c r="AK105" s="3"/>
+      <c r="AL105" s="3"/>
+      <c r="AM105" s="3"/>
+      <c r="AN105" s="3"/>
+      <c r="AO105" s="3"/>
+    </row>
+    <row r="106" spans="1:41">
+      <c r="A106" s="2"/>
+      <c r="B106" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="C106" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="D106" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="E106" s="4"/>
+      <c r="F106" s="4"/>
+      <c r="G106" s="4"/>
+      <c r="H106" s="4"/>
+      <c r="I106" s="4"/>
+      <c r="J106" s="3"/>
+      <c r="K106" s="4"/>
+      <c r="L106" s="4"/>
+      <c r="M106" s="4"/>
+      <c r="N106" s="4"/>
+      <c r="O106"/>
+      <c r="P106"/>
+      <c r="Q106"/>
+      <c r="R106"/>
+      <c r="T106" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="U106" s="4"/>
+      <c r="W106" s="4"/>
+      <c r="X106" s="4"/>
+      <c r="Y106" s="4"/>
+      <c r="Z106" s="3"/>
+      <c r="AA106" s="3"/>
+      <c r="AB106" s="3"/>
+      <c r="AC106" s="3"/>
+      <c r="AD106" s="3"/>
+      <c r="AE106" s="3"/>
+      <c r="AF106" s="3"/>
+      <c r="AG106" s="3"/>
+      <c r="AH106" s="3"/>
+      <c r="AI106" s="3"/>
+      <c r="AJ106" s="3"/>
+      <c r="AK106" s="3"/>
+      <c r="AL106" s="3"/>
+      <c r="AM106" s="3"/>
+      <c r="AN106" s="3"/>
+      <c r="AO106" s="3"/>
+    </row>
+    <row r="107" spans="1:41">
+      <c r="A107" s="2"/>
+      <c r="B107" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="C107" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="D107" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="E107" s="4"/>
+      <c r="F107" s="4"/>
+      <c r="G107" s="4"/>
+      <c r="H107" s="4"/>
+      <c r="I107" s="4"/>
+      <c r="J107" s="3"/>
+      <c r="K107" s="4"/>
+      <c r="L107" s="4"/>
+      <c r="M107" s="4"/>
+      <c r="N107" s="4"/>
+      <c r="O107"/>
+      <c r="P107"/>
+      <c r="Q107"/>
+      <c r="R107"/>
+      <c r="T107" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="U107" s="4"/>
+      <c r="W107" s="4"/>
+      <c r="X107" s="4"/>
+      <c r="Y107" s="4"/>
+      <c r="Z107" s="3"/>
+      <c r="AA107" s="3"/>
+      <c r="AB107" s="3"/>
+      <c r="AC107" s="3"/>
+      <c r="AD107" s="3"/>
+      <c r="AE107" s="3"/>
+      <c r="AF107" s="3"/>
+      <c r="AG107" s="3"/>
+      <c r="AH107" s="3"/>
+      <c r="AI107" s="3"/>
+      <c r="AJ107" s="3"/>
+      <c r="AK107" s="3"/>
+      <c r="AL107" s="3"/>
+      <c r="AM107" s="3"/>
+      <c r="AN107" s="3"/>
+      <c r="AO107" s="3"/>
+    </row>
+    <row r="108" spans="1:41">
+      <c r="A108" s="2"/>
+      <c r="B108" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="C108" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="D108" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="E108" s="4"/>
+      <c r="F108" s="4"/>
+      <c r="G108" s="4"/>
+      <c r="H108" s="4"/>
+      <c r="I108" s="4"/>
+      <c r="J108" s="3"/>
+      <c r="K108" s="4"/>
+      <c r="L108" s="4"/>
+      <c r="M108" s="4"/>
+      <c r="N108" s="4"/>
+      <c r="O108"/>
+      <c r="P108"/>
+      <c r="Q108"/>
+      <c r="R108"/>
+      <c r="T108" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="U108" s="4"/>
+      <c r="W108" s="4"/>
+      <c r="X108" s="4"/>
+      <c r="Y108" s="4"/>
+      <c r="Z108" s="3"/>
+      <c r="AA108" s="3"/>
+      <c r="AB108" s="3"/>
+      <c r="AC108" s="3"/>
+      <c r="AD108" s="3"/>
+      <c r="AE108" s="3"/>
+      <c r="AF108" s="3"/>
+      <c r="AG108" s="3"/>
+      <c r="AH108" s="3"/>
+      <c r="AI108" s="3"/>
+      <c r="AJ108" s="3"/>
+      <c r="AK108" s="3"/>
+      <c r="AL108" s="3"/>
+      <c r="AM108" s="3"/>
+      <c r="AN108" s="3"/>
+      <c r="AO108" s="3"/>
+    </row>
+    <row r="109" spans="1:41">
+      <c r="A109" s="2"/>
+      <c r="B109" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="C109" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="D109" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="E109" s="4"/>
+      <c r="F109" s="4"/>
+      <c r="G109" s="4"/>
+      <c r="H109" s="4"/>
+      <c r="I109" s="4"/>
+      <c r="J109" s="3"/>
+      <c r="K109" s="4"/>
+      <c r="L109" s="4"/>
+      <c r="M109" s="4"/>
+      <c r="N109" s="4"/>
+      <c r="O109"/>
+      <c r="P109"/>
+      <c r="Q109"/>
+      <c r="R109"/>
+      <c r="T109" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="U109" s="4"/>
+      <c r="W109" s="4"/>
+      <c r="X109" s="4"/>
+      <c r="Y109" s="4"/>
+      <c r="Z109" s="3"/>
+      <c r="AA109" s="3"/>
+      <c r="AB109" s="3"/>
+      <c r="AC109" s="3"/>
+      <c r="AD109" s="3"/>
+      <c r="AE109" s="3"/>
+      <c r="AF109" s="3"/>
+      <c r="AG109" s="3"/>
+      <c r="AH109" s="3"/>
+      <c r="AI109" s="3"/>
+      <c r="AJ109" s="3"/>
+      <c r="AK109" s="3"/>
+      <c r="AL109" s="3"/>
+      <c r="AM109" s="3"/>
+      <c r="AN109" s="3"/>
+      <c r="AO109" s="3"/>
+    </row>
+    <row r="110" spans="1:41">
+      <c r="A110" s="2"/>
+      <c r="B110" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="C110" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="D110" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="E110" s="4"/>
+      <c r="F110" s="4"/>
+      <c r="G110" s="4"/>
+      <c r="H110" s="4"/>
+      <c r="I110" s="4"/>
+      <c r="J110" s="3"/>
+      <c r="K110" s="4"/>
+      <c r="L110" s="4"/>
+      <c r="M110" s="4"/>
+      <c r="N110" s="4"/>
+      <c r="O110"/>
+      <c r="P110"/>
+      <c r="Q110"/>
+      <c r="R110"/>
+      <c r="T110" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="U110" s="4"/>
+      <c r="W110" s="4"/>
+      <c r="X110" s="4"/>
+      <c r="Y110" s="4"/>
+      <c r="Z110" s="3"/>
+      <c r="AA110" s="3"/>
+      <c r="AB110" s="3"/>
+      <c r="AC110" s="3"/>
+      <c r="AD110" s="3"/>
+      <c r="AE110" s="3"/>
+      <c r="AF110" s="3"/>
+      <c r="AG110" s="3"/>
+      <c r="AH110" s="3"/>
+      <c r="AI110" s="3"/>
+      <c r="AJ110" s="3"/>
+      <c r="AK110" s="3"/>
+      <c r="AL110" s="3"/>
+      <c r="AM110" s="3"/>
+      <c r="AN110" s="3"/>
+      <c r="AO110" s="3"/>
+    </row>
+    <row r="111" spans="1:41">
+      <c r="A111" s="2"/>
+      <c r="B111" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="C111" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="D111" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="E111" s="4"/>
+      <c r="F111" s="4"/>
+      <c r="G111" s="4"/>
+      <c r="H111" s="4"/>
+      <c r="I111" s="4"/>
+      <c r="J111" s="3"/>
+      <c r="K111" s="4"/>
+      <c r="L111" s="4"/>
+      <c r="M111" s="4"/>
+      <c r="N111" s="4"/>
+      <c r="O111"/>
+      <c r="P111"/>
+      <c r="Q111"/>
+      <c r="R111"/>
+      <c r="T111" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="U111" s="4"/>
+      <c r="W111" s="4"/>
+      <c r="X111" s="4"/>
+      <c r="Y111" s="4"/>
+      <c r="Z111" s="3"/>
+      <c r="AA111" s="3"/>
+      <c r="AB111" s="3"/>
+      <c r="AC111" s="3"/>
+      <c r="AD111" s="3"/>
+      <c r="AE111" s="3"/>
+      <c r="AF111" s="3"/>
+      <c r="AG111" s="3"/>
+      <c r="AH111" s="3"/>
+      <c r="AI111" s="3"/>
+      <c r="AJ111" s="3"/>
+      <c r="AK111" s="3"/>
+      <c r="AL111" s="3"/>
+      <c r="AM111" s="3"/>
+      <c r="AN111" s="3"/>
+      <c r="AO111" s="3"/>
+    </row>
+    <row r="112" spans="1:41">
+      <c r="A112" s="2"/>
+      <c r="B112" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="C112" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="D112" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="E112" s="4"/>
+      <c r="F112" s="4"/>
+      <c r="G112" s="4"/>
+      <c r="H112" s="4"/>
+      <c r="I112" s="4"/>
+      <c r="J112" s="3"/>
+      <c r="K112" s="4"/>
+      <c r="L112" s="4"/>
+      <c r="M112" s="4"/>
+      <c r="N112" s="4"/>
+      <c r="O112"/>
+      <c r="P112"/>
+      <c r="Q112"/>
+      <c r="R112"/>
+      <c r="T112" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="U112" s="4"/>
+      <c r="W112" s="4"/>
+      <c r="X112" s="4"/>
+      <c r="Y112" s="4"/>
+      <c r="Z112" s="3"/>
+      <c r="AA112" s="3"/>
+      <c r="AB112" s="3"/>
+      <c r="AC112" s="3"/>
+      <c r="AD112" s="3"/>
+      <c r="AE112" s="3"/>
+      <c r="AF112" s="3"/>
+      <c r="AG112" s="3"/>
+      <c r="AH112" s="3"/>
+      <c r="AI112" s="3"/>
+      <c r="AJ112" s="3"/>
+      <c r="AK112" s="3"/>
+      <c r="AL112" s="3"/>
+      <c r="AM112" s="3"/>
+      <c r="AN112" s="3"/>
+      <c r="AO112" s="3"/>
+    </row>
+    <row r="113" spans="1:41">
+      <c r="A113" s="2"/>
+      <c r="B113" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="C113" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="D113" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="E113" s="4"/>
+      <c r="F113" s="4"/>
+      <c r="G113" s="4"/>
+      <c r="H113" s="4"/>
+      <c r="I113" s="4"/>
+      <c r="J113" s="3"/>
+      <c r="K113" s="4"/>
+      <c r="L113" s="4"/>
+      <c r="M113" s="4"/>
+      <c r="N113" s="4"/>
+      <c r="O113"/>
+      <c r="P113"/>
+      <c r="Q113"/>
+      <c r="R113"/>
+      <c r="T113" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="U113" s="4"/>
+      <c r="W113" s="4"/>
+      <c r="X113" s="4"/>
+      <c r="Y113" s="4"/>
+      <c r="Z113" s="3"/>
+      <c r="AA113" s="3"/>
+      <c r="AB113" s="3"/>
+      <c r="AC113" s="3"/>
+      <c r="AD113" s="3"/>
+      <c r="AE113" s="3"/>
+      <c r="AF113" s="3"/>
+      <c r="AG113" s="3"/>
+      <c r="AH113" s="3"/>
+      <c r="AI113" s="3"/>
+      <c r="AJ113" s="3"/>
+      <c r="AK113" s="3"/>
+      <c r="AL113" s="3"/>
+      <c r="AM113" s="3"/>
+      <c r="AN113" s="3"/>
+      <c r="AO113" s="3"/>
+    </row>
+    <row r="114" spans="1:41">
+      <c r="A114" s="2"/>
+      <c r="B114" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="C114" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="D114" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="E114" s="4"/>
+      <c r="F114" s="4"/>
+      <c r="G114" s="4"/>
+      <c r="H114" s="4"/>
+      <c r="I114" s="4"/>
+      <c r="J114" s="3"/>
+      <c r="K114" s="4"/>
+      <c r="L114" s="4"/>
+      <c r="M114" s="4"/>
+      <c r="N114" s="4"/>
+      <c r="O114"/>
+      <c r="P114"/>
+      <c r="Q114"/>
+      <c r="R114"/>
+      <c r="T114" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="U114" s="4"/>
+      <c r="W114" s="4"/>
+      <c r="X114" s="4"/>
+      <c r="Y114" s="4"/>
+      <c r="Z114" s="3"/>
+      <c r="AA114" s="3"/>
+      <c r="AB114" s="3"/>
+      <c r="AC114" s="3"/>
+      <c r="AD114" s="3"/>
+      <c r="AE114" s="3"/>
+      <c r="AF114" s="3"/>
+      <c r="AG114" s="3"/>
+      <c r="AH114" s="3"/>
+      <c r="AI114" s="3"/>
+      <c r="AJ114" s="3"/>
+      <c r="AK114" s="3"/>
+      <c r="AL114" s="3"/>
+      <c r="AM114" s="3"/>
+      <c r="AN114" s="3"/>
+      <c r="AO114" s="3"/>
+    </row>
+    <row r="115" spans="1:41">
+      <c r="A115" s="2"/>
+      <c r="B115" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="C115" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="D115" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="E115" s="4"/>
+      <c r="F115" s="4"/>
+      <c r="G115" s="4"/>
+      <c r="H115" s="4"/>
+      <c r="I115" s="4"/>
+      <c r="J115" s="3"/>
+      <c r="K115" s="4"/>
+      <c r="L115" s="4"/>
+      <c r="M115" s="4"/>
+      <c r="N115" s="4"/>
+      <c r="O115"/>
+      <c r="P115"/>
+      <c r="Q115"/>
+      <c r="R115"/>
+      <c r="T115" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="U115" s="4"/>
+      <c r="W115" s="4"/>
+      <c r="X115" s="4"/>
+      <c r="Y115" s="4"/>
+      <c r="Z115" s="3"/>
+      <c r="AA115" s="3"/>
+      <c r="AB115" s="3"/>
+      <c r="AC115" s="3"/>
+      <c r="AD115" s="3"/>
+      <c r="AE115" s="3"/>
+      <c r="AF115" s="3"/>
+      <c r="AG115" s="3"/>
+      <c r="AH115" s="3"/>
+      <c r="AI115" s="3"/>
+      <c r="AJ115" s="3"/>
+      <c r="AK115" s="3"/>
+      <c r="AL115" s="3"/>
+      <c r="AM115" s="3"/>
+      <c r="AN115" s="3"/>
+      <c r="AO115" s="3"/>
+    </row>
+    <row r="116" spans="1:41">
+      <c r="A116" s="2"/>
+      <c r="B116" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="C116" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="D116" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="E116" s="4"/>
+      <c r="F116" s="4"/>
+      <c r="G116" s="4"/>
+      <c r="H116" s="4"/>
+      <c r="I116" s="4"/>
+      <c r="J116" s="3"/>
+      <c r="K116" s="4"/>
+      <c r="L116" s="4"/>
+      <c r="M116" s="4"/>
+      <c r="N116" s="4"/>
+      <c r="O116"/>
+      <c r="P116"/>
+      <c r="Q116"/>
+      <c r="R116"/>
+      <c r="T116" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="U116" s="4"/>
+      <c r="W116" s="4"/>
+      <c r="X116" s="4"/>
+      <c r="Y116" s="4"/>
+      <c r="Z116" s="3"/>
+      <c r="AA116" s="3"/>
+      <c r="AB116" s="3"/>
+      <c r="AC116" s="3"/>
+      <c r="AD116" s="3"/>
+      <c r="AE116" s="3"/>
+      <c r="AF116" s="3"/>
+      <c r="AG116" s="3"/>
+      <c r="AH116" s="3"/>
+      <c r="AI116" s="3"/>
+      <c r="AJ116" s="3"/>
+      <c r="AK116" s="3"/>
+      <c r="AL116" s="3"/>
+      <c r="AM116" s="3"/>
+      <c r="AN116" s="3"/>
+      <c r="AO116" s="3"/>
+    </row>
+    <row r="117" spans="1:41">
+      <c r="A117" s="2"/>
+      <c r="B117" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="C117" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="D117" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="E117" s="4"/>
+      <c r="F117" s="4"/>
+      <c r="G117" s="4"/>
+      <c r="H117" s="4"/>
+      <c r="I117" s="4"/>
+      <c r="J117" s="3"/>
+      <c r="K117" s="4"/>
+      <c r="L117" s="4"/>
+      <c r="M117" s="4"/>
+      <c r="N117" s="4"/>
+      <c r="O117"/>
+      <c r="P117"/>
+      <c r="Q117"/>
+      <c r="R117"/>
+      <c r="T117" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="U117" s="4"/>
+      <c r="W117" s="4"/>
+      <c r="X117" s="4"/>
+      <c r="Y117" s="4"/>
+      <c r="Z117" s="3"/>
+      <c r="AA117" s="3"/>
+      <c r="AB117" s="3"/>
+      <c r="AC117" s="3"/>
+      <c r="AD117" s="3"/>
+      <c r="AE117" s="3"/>
+      <c r="AF117" s="3"/>
+      <c r="AG117" s="3"/>
+      <c r="AH117" s="3"/>
+      <c r="AI117" s="3"/>
+      <c r="AJ117" s="3"/>
+      <c r="AK117" s="3"/>
+      <c r="AL117" s="3"/>
+      <c r="AM117" s="3"/>
+      <c r="AN117" s="3"/>
+      <c r="AO117" s="3"/>
+    </row>
+    <row r="118" spans="1:41">
+      <c r="A118" s="2"/>
+      <c r="B118" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="C118" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="D118" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="E118" s="4"/>
+      <c r="F118" s="4"/>
+      <c r="G118" s="4"/>
+      <c r="H118" s="4"/>
+      <c r="I118" s="4"/>
+      <c r="J118" s="3"/>
+      <c r="K118" s="4"/>
+      <c r="L118" s="4"/>
+      <c r="M118" s="4"/>
+      <c r="N118" s="4"/>
+      <c r="O118"/>
+      <c r="P118"/>
+      <c r="Q118"/>
+      <c r="R118"/>
+      <c r="T118" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="U118" s="4"/>
+      <c r="W118" s="4"/>
+      <c r="X118" s="4"/>
+      <c r="Y118" s="4"/>
+      <c r="Z118" s="3"/>
+      <c r="AA118" s="3"/>
+      <c r="AB118" s="3"/>
+      <c r="AC118" s="3"/>
+      <c r="AD118" s="3"/>
+      <c r="AE118" s="3"/>
+      <c r="AF118" s="3"/>
+      <c r="AG118" s="3"/>
+      <c r="AH118" s="3"/>
+      <c r="AI118" s="3"/>
+      <c r="AJ118" s="3"/>
+      <c r="AK118" s="3"/>
+      <c r="AL118" s="3"/>
+      <c r="AM118" s="3"/>
+      <c r="AN118" s="3"/>
+      <c r="AO118" s="3"/>
+    </row>
+    <row r="119" spans="1:41">
+      <c r="A119" s="2"/>
+      <c r="B119" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="C119" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="D119" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="E119" s="4"/>
+      <c r="F119" s="4"/>
+      <c r="G119" s="4"/>
+      <c r="H119" s="4"/>
+      <c r="I119" s="4"/>
+      <c r="J119" s="3"/>
+      <c r="K119" s="4"/>
+      <c r="L119" s="4"/>
+      <c r="M119" s="4"/>
+      <c r="N119" s="4"/>
+      <c r="O119"/>
+      <c r="P119"/>
+      <c r="Q119"/>
+      <c r="R119"/>
+      <c r="T119" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="U119" s="4"/>
+      <c r="W119" s="4"/>
+      <c r="X119" s="4"/>
+      <c r="Y119" s="4"/>
+      <c r="Z119" s="3"/>
+      <c r="AA119" s="3"/>
+      <c r="AB119" s="3"/>
+      <c r="AC119" s="3"/>
+      <c r="AD119" s="3"/>
+      <c r="AE119" s="3"/>
+      <c r="AF119" s="3"/>
+      <c r="AG119" s="3"/>
+      <c r="AH119" s="3"/>
+      <c r="AI119" s="3"/>
+      <c r="AJ119" s="3"/>
+      <c r="AK119" s="3"/>
+      <c r="AL119" s="3"/>
+      <c r="AM119" s="3"/>
+      <c r="AN119" s="3"/>
+      <c r="AO119" s="3"/>
+    </row>
+    <row r="120" spans="1:41">
+      <c r="A120" s="2"/>
+      <c r="B120" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="C120" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="D120" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="E120" s="4"/>
+      <c r="F120" s="4"/>
+      <c r="G120" s="4"/>
+      <c r="H120" s="4"/>
+      <c r="I120" s="4"/>
+      <c r="J120" s="3"/>
+      <c r="K120" s="4"/>
+      <c r="L120" s="4"/>
+      <c r="M120" s="4"/>
+      <c r="N120" s="4"/>
+      <c r="O120"/>
+      <c r="P120"/>
+      <c r="Q120"/>
+      <c r="R120"/>
+      <c r="T120" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="U120" s="4"/>
+      <c r="W120" s="4"/>
+      <c r="X120" s="4"/>
+      <c r="Y120" s="4"/>
+      <c r="Z120" s="3"/>
+      <c r="AA120" s="3"/>
+      <c r="AB120" s="3"/>
+      <c r="AC120" s="3"/>
+      <c r="AD120" s="3"/>
+      <c r="AE120" s="3"/>
+      <c r="AF120" s="3"/>
+      <c r="AG120" s="3"/>
+      <c r="AH120" s="3"/>
+      <c r="AI120" s="3"/>
+      <c r="AJ120" s="3"/>
+      <c r="AK120" s="3"/>
+      <c r="AL120" s="3"/>
+      <c r="AM120" s="3"/>
+      <c r="AN120" s="3"/>
+      <c r="AO120" s="3"/>
+    </row>
+    <row r="121" spans="1:41">
+      <c r="A121" s="2"/>
+      <c r="B121" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="C121" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="D121" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="E121" s="4"/>
+      <c r="F121" s="4"/>
+      <c r="G121" s="4"/>
+      <c r="H121" s="4"/>
+      <c r="I121" s="4"/>
+      <c r="J121" s="3"/>
+      <c r="K121" s="4"/>
+      <c r="L121" s="4"/>
+      <c r="M121" s="4"/>
+      <c r="N121" s="4"/>
+      <c r="O121"/>
+      <c r="P121"/>
+      <c r="Q121"/>
+      <c r="R121"/>
+      <c r="T121" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="U121" s="4"/>
+      <c r="W121" s="4"/>
+      <c r="X121" s="4"/>
+      <c r="Y121" s="4"/>
+      <c r="Z121" s="3"/>
+      <c r="AA121" s="3"/>
+      <c r="AB121" s="3"/>
+      <c r="AC121" s="3"/>
+      <c r="AD121" s="3"/>
+      <c r="AE121" s="3"/>
+      <c r="AF121" s="3"/>
+      <c r="AG121" s="3"/>
+      <c r="AH121" s="3"/>
+      <c r="AI121" s="3"/>
+      <c r="AJ121" s="3"/>
+      <c r="AK121" s="3"/>
+      <c r="AL121" s="3"/>
+      <c r="AM121" s="3"/>
+      <c r="AN121" s="3"/>
+      <c r="AO121" s="3"/>
+    </row>
+    <row r="122" spans="1:41">
+      <c r="A122" s="2"/>
+      <c r="B122" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="C122" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="D122" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="E122" s="4"/>
+      <c r="F122" s="4"/>
+      <c r="G122" s="4"/>
+      <c r="H122" s="4"/>
+      <c r="I122" s="4"/>
+      <c r="J122" s="3"/>
+      <c r="K122" s="4"/>
+      <c r="L122" s="4"/>
+      <c r="M122" s="4"/>
+      <c r="N122" s="4"/>
+      <c r="O122"/>
+      <c r="P122"/>
+      <c r="Q122"/>
+      <c r="R122"/>
+      <c r="T122" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="U122" s="4"/>
+      <c r="W122" s="4"/>
+      <c r="X122" s="4"/>
+      <c r="Y122" s="4"/>
+      <c r="Z122" s="3"/>
+      <c r="AA122" s="3"/>
+      <c r="AB122" s="3"/>
+      <c r="AC122" s="3"/>
+      <c r="AD122" s="3"/>
+      <c r="AE122" s="3"/>
+      <c r="AF122" s="3"/>
+      <c r="AG122" s="3"/>
+      <c r="AH122" s="3"/>
+      <c r="AI122" s="3"/>
+      <c r="AJ122" s="3"/>
+      <c r="AK122" s="3"/>
+      <c r="AL122" s="3"/>
+      <c r="AM122" s="3"/>
+      <c r="AN122" s="3"/>
+      <c r="AO122" s="3"/>
+    </row>
+    <row r="123" spans="1:41">
+      <c r="A123" s="2"/>
+      <c r="B123" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="C123" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="D123" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="E123" s="4"/>
+      <c r="F123" s="4"/>
+      <c r="G123" s="4"/>
+      <c r="H123" s="4"/>
+      <c r="I123" s="4"/>
+      <c r="J123" s="3"/>
+      <c r="K123" s="4"/>
+      <c r="L123" s="4"/>
+      <c r="M123" s="4"/>
+      <c r="N123" s="4"/>
+      <c r="O123"/>
+      <c r="P123"/>
+      <c r="Q123"/>
+      <c r="R123"/>
+      <c r="T123" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="U123" s="4"/>
+      <c r="W123" s="4"/>
+      <c r="X123" s="4"/>
+      <c r="Y123" s="4"/>
+      <c r="Z123" s="3"/>
+      <c r="AA123" s="3"/>
+      <c r="AB123" s="3"/>
+      <c r="AC123" s="3"/>
+      <c r="AD123" s="3"/>
+      <c r="AE123" s="3"/>
+      <c r="AF123" s="3"/>
+      <c r="AG123" s="3"/>
+      <c r="AH123" s="3"/>
+      <c r="AI123" s="3"/>
+      <c r="AJ123" s="3"/>
+      <c r="AK123" s="3"/>
+      <c r="AL123" s="3"/>
+      <c r="AM123" s="3"/>
+      <c r="AN123" s="3"/>
+      <c r="AO123" s="3"/>
+    </row>
+    <row r="124" spans="36:37">
+      <c r="AJ124" s="3"/>
+      <c r="AK124" s="3"/>
+    </row>
+    <row r="125" spans="36:37">
+      <c r="AJ125" s="3"/>
+      <c r="AK125" s="3"/>
     </row>
   </sheetData>
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J58:J79 J80:J123 AB58:AB79 AB80:AB123 AH58:AJ79 AH80:AJ123">
+      <formula1>"是,否"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X58:Y79 X80:Y123">
+      <formula1>"DI,AI,DO,AO"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="A1:C12 A13:C54 I1:I54" numberStoredAsText="1"/>
+    <ignoredError sqref="I1:I11 I12:I21 A1:C11 A12:C21" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>